--- a/data/seed/portfolio/L-2025-8298/vypiska_2026-07_09.xlsx
+++ b/data/seed/portfolio/L-2025-8298/vypiska_2026-07_09.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J181"/>
+  <dimension ref="A1:J189"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -542,21 +542,21 @@
       </c>
       <c r="C8" s="2" t="n"/>
       <c r="D8" s="2" t="n">
-        <v>304738000</v>
+        <v>85101000</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Saodat Meva-Sabzavot MChJ</t>
+          <t>Zarafshon Poligraf MChJ</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>352568163</t>
+          <t>331756684</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>20208000856244453001</t>
+          <t>20208000798127163001</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -566,11 +566,11 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Shartnoma №59/26 bo'yicha oldindan to'lov</t>
+          <t>Предоплата за товар по договору №127/26 от 01.07.2026</t>
         </is>
       </c>
       <c r="J8" s="2" t="n">
-        <v>580438000</v>
+        <v>360801000</v>
       </c>
     </row>
     <row r="9">
@@ -582,61 +582,56 @@
       </c>
       <c r="C9" s="2" t="n"/>
       <c r="D9" s="2" t="n">
-        <v>24905000</v>
+        <v>9984000</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Nihol Qurilish Materiallari MChJ</t>
+          <t>Zarafshon Poligraf MChJ</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>246317566</t>
+          <t>331756684</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>20208000447981271001</t>
+          <t>20208000798127163001</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №17/26, QQS 12%</t>
+          <t>Оплата за продукцию по дог. №239/26, НДС 12%</t>
         </is>
       </c>
       <c r="J9" s="2" t="n">
-        <v>605343000</v>
+        <v>370785000</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="n">
-        <v>46204</v>
+        <v>46208</v>
       </c>
       <c r="B10" t="n">
         <v>102</v>
       </c>
-      <c r="C10" s="2" t="n"/>
-      <c r="D10" s="2" t="n">
-        <v>9472000</v>
-      </c>
+      <c r="C10" s="2" t="n">
+        <v>102400000</v>
+      </c>
+      <c r="D10" s="2" t="n"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Saodat Meva-Sabzavot MChJ</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>352568163</t>
+          <t>Kreditni qaytarish hisobvarag'i (L-2025-8298)</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>20208000856244453001</t>
+          <t>16307000227552595417</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -646,117 +641,117 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>ПРЕДОПЛАТА ЗА ТОВАР ПО ДОГОВОРУ №86/26 ОТ 01.07.2026</t>
+          <t>Kredit shartnomasi L-2025-8298 bo'yicha navbatdagi to'lov (07.2026)</t>
         </is>
       </c>
       <c r="J10" s="2" t="n">
-        <v>614815000</v>
+        <v>268385000</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="n">
-        <v>46204</v>
+        <v>46209</v>
       </c>
       <c r="B11" t="n">
         <v>103</v>
       </c>
-      <c r="C11" s="2" t="n">
-        <v>68578000</v>
-      </c>
-      <c r="D11" s="2" t="n"/>
+      <c r="C11" s="2" t="n"/>
+      <c r="D11" s="2" t="n">
+        <v>69999000</v>
+      </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Gulshan Poligraf MChJ</t>
+          <t>Navro'z Agro MChJ</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>321061342</t>
+          <t>256816338</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>20208000490421029001</t>
+          <t>20208000624445379001</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Transport xizmatlari uchun to'lov, shartnoma №170/26</t>
+          <t>ОПЛАТА ЗА ТОВАР ПО С/Ф №8828 ОТ 06.07.2026, В Т.Ч. НДС 12%</t>
         </is>
       </c>
       <c r="J11" s="2" t="n">
-        <v>546237000</v>
+        <v>338384000</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="n">
-        <v>46205</v>
+        <v>46209</v>
       </c>
       <c r="B12" t="n">
         <v>104</v>
       </c>
-      <c r="C12" s="2" t="n">
-        <v>67886000</v>
-      </c>
-      <c r="D12" s="2" t="n"/>
+      <c r="C12" s="2" t="n"/>
+      <c r="D12" s="2" t="n">
+        <v>40535000</v>
+      </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Andijon Tur Servis MChJ</t>
+          <t>Navro'z Agro MChJ</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>303911698</t>
+          <t>256816338</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>20208000572864151001</t>
+          <t>20208000624445379001</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Transport xizmatlari uchun to'lov, shartnoma №162/26</t>
+          <t>Оплата за товар по счет-фактуре №7344 от 06.07.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J12" s="2" t="n">
-        <v>478351000</v>
+        <v>378919000</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="n">
-        <v>46206</v>
+        <v>46209</v>
       </c>
       <c r="B13" t="n">
         <v>105</v>
       </c>
-      <c r="C13" s="2" t="n">
-        <v>34032000</v>
-      </c>
-      <c r="D13" s="2" t="n"/>
+      <c r="C13" s="2" t="n"/>
+      <c r="D13" s="2" t="n">
+        <v>36199000</v>
+      </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Gulshan Poligraf MChJ</t>
+          <t>Zarafshon Poligraf MChJ</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>321061342</t>
+          <t>331756684</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>20208000490421029001</t>
+          <t>20208000798127163001</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -766,32 +761,37 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Tovarlar uchun to'lov h/f №8205</t>
+          <t>Оплата за товар по счет-фактуре №9154 от 06.07.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J13" s="2" t="n">
-        <v>444319000</v>
+        <v>415118000</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="n">
-        <v>46208</v>
+        <v>46209</v>
       </c>
       <c r="B14" t="n">
         <v>106</v>
       </c>
-      <c r="C14" s="2" t="n">
-        <v>102400000</v>
-      </c>
-      <c r="D14" s="2" t="n"/>
+      <c r="C14" s="2" t="n"/>
+      <c r="D14" s="2" t="n">
+        <v>21101000</v>
+      </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Kreditni qaytarish hisobvarag'i (L-2025-8298)</t>
+          <t>Zarafshon Poligraf MChJ</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>331756684</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>16307000227552595417</t>
+          <t>20208000798127163001</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -801,11 +801,11 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Kredit shartnomasi L-2025-8298 bo'yicha navbatdagi to'lov (07.2026)</t>
+          <t>Оплата по с/ф №1083 за поставленный товар</t>
         </is>
       </c>
       <c r="J14" s="2" t="n">
-        <v>341919000</v>
+        <v>436219000</v>
       </c>
     </row>
     <row r="15">
@@ -815,23 +815,23 @@
       <c r="B15" t="n">
         <v>107</v>
       </c>
-      <c r="C15" s="2" t="n"/>
-      <c r="D15" s="2" t="n">
-        <v>143147000</v>
-      </c>
+      <c r="C15" s="2" t="n">
+        <v>16549000</v>
+      </c>
+      <c r="D15" s="2" t="n"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Nihol Qurilish Materiallari MChJ</t>
+          <t>Yangi Hayot Sut Mahsulotlari MChJ</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>246317566</t>
+          <t>206134234</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>20208000447981271001</t>
+          <t>20208000042102996001</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -841,11 +841,11 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>ПРЕДОПЛАТА ЗА ТОВАР ПО ДГОВОРУ №111/26 ОТ 06.07.2026</t>
+          <t>Оплата за сырье по договору №270/26 от 06.07.2026, НДС 12%</t>
         </is>
       </c>
       <c r="J15" s="2" t="n">
-        <v>485066000</v>
+        <v>419670000</v>
       </c>
     </row>
     <row r="16">
@@ -855,37 +855,37 @@
       <c r="B16" t="n">
         <v>108</v>
       </c>
-      <c r="C16" s="2" t="n"/>
-      <c r="D16" s="2" t="n">
-        <v>15789000</v>
-      </c>
+      <c r="C16" s="2" t="n">
+        <v>17235000</v>
+      </c>
+      <c r="D16" s="2" t="n"/>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Nihol Qurilish Materiallari MChJ</t>
+          <t>Oqtosh Agro Servis MChJ</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>246317566</t>
+          <t>277163738</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>20208000447981271001</t>
+          <t>20208000017612936001</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №4204</t>
+          <t>Оплата за сырье по договору №114/26 от 06.07.2026, НДС 12%</t>
         </is>
       </c>
       <c r="J16" s="2" t="n">
-        <v>500855000</v>
+        <v>402435000</v>
       </c>
     </row>
     <row r="17">
@@ -896,297 +896,297 @@
         <v>109</v>
       </c>
       <c r="C17" s="2" t="n">
-        <v>27713000</v>
+        <v>112409000</v>
       </c>
       <c r="D17" s="2" t="n"/>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Andijon Tur Servis MChJ</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>303911698</t>
+          <t>Zarafshon Kredit Bank</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>20208000572864151001</t>
+          <t>45994000900000001001</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Оплата за упаковочные материалы, с/ф №575</t>
+          <t>Перечисление заработной платы за июнь 2026 г. согласно реестру №7660</t>
         </is>
       </c>
       <c r="J17" s="2" t="n">
-        <v>473142000</v>
+        <v>290026000</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="n">
-        <v>46209</v>
+        <v>46210</v>
       </c>
       <c r="B18" t="n">
         <v>110</v>
       </c>
       <c r="C18" s="2" t="n">
-        <v>45117000</v>
+        <v>8936000</v>
       </c>
       <c r="D18" s="2" t="n"/>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Gulshan Poligraf MChJ</t>
+          <t>Shodlik Qurilish MChJ</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>321061342</t>
+          <t>354336802</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>20208000490421029001</t>
+          <t>20208000212400074001</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Tovarlar uchun to'lov h/f №9350</t>
+          <t>Аренда помещения за июль, дог. №93/24</t>
         </is>
       </c>
       <c r="J18" s="2" t="n">
-        <v>428025000</v>
+        <v>281090000</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="n">
-        <v>46209</v>
+        <v>46213</v>
       </c>
       <c r="B19" t="n">
         <v>111</v>
       </c>
-      <c r="C19" s="2" t="n">
-        <v>112409000</v>
-      </c>
-      <c r="D19" s="2" t="n"/>
+      <c r="C19" s="2" t="n"/>
+      <c r="D19" s="2" t="n">
+        <v>16165000</v>
+      </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Zarafshon Kredit Bank</t>
+          <t>Qo'qon Mato MChJ</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>359614862</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>45994000900000001001</t>
+          <t>20208000130507081001</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Iyun oyi uchun ish haqi, reestr №8271</t>
+          <t>Оплата за товар по счет-фактуре №7652 от 10.07.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J19" s="2" t="n">
-        <v>315616000</v>
+        <v>297255000</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="n">
-        <v>46210</v>
+        <v>46213</v>
       </c>
       <c r="B20" t="n">
         <v>112</v>
       </c>
       <c r="C20" s="2" t="n"/>
       <c r="D20" s="2" t="n">
-        <v>33123000</v>
+        <v>10812000</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Nihol Qurilish Materiallari MChJ</t>
+          <t>Zarafshon Poligraf MChJ</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>246317566</t>
+          <t>331756684</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>20208000447981271001</t>
+          <t>20208000798127163001</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №30/26 от 07.07.2026</t>
+          <t>Shartnoma №238/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
       <c r="J20" s="2" t="n">
-        <v>348739000</v>
+        <v>308067000</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="n">
-        <v>46210</v>
+        <v>46213</v>
       </c>
       <c r="B21" t="n">
         <v>113</v>
       </c>
       <c r="C21" s="2" t="n">
-        <v>8936000</v>
+        <v>43158000</v>
       </c>
       <c r="D21" s="2" t="n"/>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Ilhom Qurilish Materiallari AJ</t>
+          <t>Farg'ona Metall Servis MChJ</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>372723361</t>
+          <t>244700213</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>20208000768964202001</t>
+          <t>20208000483988736001</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Bino ijarasi uchun to'lov iyul</t>
+          <t>Предоплата за материалы по договору №125/26</t>
         </is>
       </c>
       <c r="J21" s="2" t="n">
-        <v>339803000</v>
+        <v>264909000</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="n">
-        <v>46212</v>
+        <v>46216</v>
       </c>
       <c r="B22" t="n">
         <v>114</v>
       </c>
       <c r="C22" s="2" t="n"/>
       <c r="D22" s="2" t="n">
-        <v>12714000</v>
+        <v>37177000</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Oltin Vodiy Mebel MChJ</t>
+          <t>Navro'z Agro MChJ</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>297197550</t>
+          <t>256816338</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>20208000006090507001</t>
+          <t>20208000624445379001</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №8283 09.07.2026, QQS bilan</t>
+          <t>ОПЛАТА ЗА ТОВАР ПО С/Ф №8481 ОТ 13.07.2026, В Т.Ч. НДС 12%</t>
         </is>
       </c>
       <c r="J22" s="2" t="n">
-        <v>352517000</v>
+        <v>302086000</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="n">
-        <v>46212</v>
+        <v>46216</v>
       </c>
       <c r="B23" t="n">
         <v>115</v>
       </c>
-      <c r="C23" s="2" t="n">
-        <v>44154000</v>
-      </c>
-      <c r="D23" s="2" t="n"/>
+      <c r="C23" s="2" t="n"/>
+      <c r="D23" s="2" t="n">
+        <v>29667000</v>
+      </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Namangan Savdo MChJ</t>
+          <t>Navro'z Agro MChJ</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>285433680</t>
+          <t>256816338</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>20208000021240007001</t>
+          <t>20208000624445379001</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Materiallar uchun oldindan to'lov, shartnoma №170/26</t>
+          <t>Оплата за товар по счет-фактуре №2920 от 13.07.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J23" s="2" t="n">
-        <v>308363000</v>
+        <v>331753000</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="n">
-        <v>46213</v>
+        <v>46216</v>
       </c>
       <c r="B24" t="n">
         <v>116</v>
       </c>
-      <c r="C24" s="2" t="n">
-        <v>81668000</v>
-      </c>
-      <c r="D24" s="2" t="n"/>
+      <c r="C24" s="2" t="n"/>
+      <c r="D24" s="2" t="n">
+        <v>22383000</v>
+      </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Gulshan Poligraf MChJ</t>
+          <t>Nukus Sut AJ</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>321061342</t>
+          <t>206223363</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>20208000490421029001</t>
+          <t>20208000104436429001</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1196,11 +1196,11 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Materiallar uchun oldindan to'lov, shartnoma №86/26</t>
+          <t>MAHSULOT UCHUN TO'LOV, SHARTNOMA №224/26, QQS 12%</t>
         </is>
       </c>
       <c r="J24" s="2" t="n">
-        <v>226695000</v>
+        <v>354136000</v>
       </c>
     </row>
     <row r="25">
@@ -1212,21 +1212,21 @@
       </c>
       <c r="C25" s="2" t="n"/>
       <c r="D25" s="2" t="n">
-        <v>69539000</v>
+        <v>18109000</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Saodat Meva-Sabzavot MChJ</t>
+          <t>Zarafshon Poligraf MChJ</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>352568163</t>
+          <t>331756684</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>20208000856244453001</t>
+          <t>20208000798127163001</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1236,11 +1236,11 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №933 13.07.2026, QQS bilan</t>
+          <t>Оплата за продукцию по договору №27/26, НДС 12%</t>
         </is>
       </c>
       <c r="J25" s="2" t="n">
-        <v>296234000</v>
+        <v>372245000</v>
       </c>
     </row>
     <row r="26">
@@ -1250,143 +1250,143 @@
       <c r="B26" t="n">
         <v>118</v>
       </c>
-      <c r="C26" s="2" t="n"/>
-      <c r="D26" s="2" t="n">
-        <v>30378000</v>
-      </c>
+      <c r="C26" s="2" t="n">
+        <v>38276000</v>
+      </c>
+      <c r="D26" s="2" t="n"/>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Nihol Qurilish Materiallari MChJ</t>
+          <t>Farg'ona Metall Servis MChJ</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>246317566</t>
+          <t>244700213</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>20208000447981271001</t>
+          <t>20208000483988736001</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №102/26, НДС 12%</t>
+          <t>Оплата за сырье по договору №110/26 от 13.07.2026, НДС 12%</t>
         </is>
       </c>
       <c r="J26" s="2" t="n">
-        <v>326612000</v>
+        <v>333969000</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="n">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="B27" t="n">
         <v>119</v>
       </c>
       <c r="C27" s="2" t="n"/>
       <c r="D27" s="2" t="n">
-        <v>17242000</v>
+        <v>25444000</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Oltin Vodiy Mebel MChJ</t>
+          <t>Navro'z Agro MChJ</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>297197550</t>
+          <t>256816338</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>20208000006090507001</t>
+          <t>20208000624445379001</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №204/26, QQS 12%</t>
+          <t>Оплата по счет-фактуре №777 за поставленный товар</t>
         </is>
       </c>
       <c r="J27" s="2" t="n">
-        <v>343854000</v>
+        <v>359413000</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="n">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="B28" t="n">
         <v>120</v>
       </c>
       <c r="C28" s="2" t="n"/>
       <c r="D28" s="2" t="n">
-        <v>8158000</v>
+        <v>11592000</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Nihol Yog'och MChJ</t>
+          <t>Zarafshon Poligraf MChJ</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>216503395</t>
+          <t>331756684</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>20208000488704236001</t>
+          <t>20208000798127163001</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №4135</t>
+          <t>Оплата по счет-фактуре №3932 за поставленный товар</t>
         </is>
       </c>
       <c r="J28" s="2" t="n">
-        <v>352012000</v>
+        <v>371005000</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="n">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="B29" t="n">
         <v>121</v>
       </c>
-      <c r="C29" s="2" t="n">
-        <v>78846000</v>
-      </c>
-      <c r="D29" s="2" t="n"/>
+      <c r="C29" s="2" t="n"/>
+      <c r="D29" s="2" t="n">
+        <v>10632000</v>
+      </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Gulshan Poligraf MChJ</t>
+          <t>Zarafshon Poligraf MChJ</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>321061342</t>
+          <t>331756684</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>20208000490421029001</t>
+          <t>20208000798127163001</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -1396,51 +1396,51 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>Xom ashyo uchun to'lov, shartnoma №32/26, QQS bilan</t>
+          <t>Предоплата за товар по договору №173/26 от 14.07.2026</t>
         </is>
       </c>
       <c r="J29" s="2" t="n">
-        <v>273166000</v>
+        <v>381637000</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="n">
-        <v>46216</v>
+        <v>46218</v>
       </c>
       <c r="B30" t="n">
         <v>122</v>
       </c>
-      <c r="C30" s="2" t="n">
-        <v>128946000</v>
-      </c>
-      <c r="D30" s="2" t="n"/>
+      <c r="C30" s="2" t="n"/>
+      <c r="D30" s="2" t="n">
+        <v>19580000</v>
+      </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Gulshan Poligraf MChJ</t>
+          <t>Sarbon Mebel XK</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>321061342</t>
+          <t>202761813</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>20208000490421029001</t>
+          <t>20208000539456465001</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>Оплата за упаковочные материалы, с/ф №6322</t>
+          <t>Shartnoma №237/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
       <c r="J30" s="2" t="n">
-        <v>144220000</v>
+        <v>401217000</v>
       </c>
     </row>
     <row r="31">
@@ -1452,35 +1452,35 @@
       </c>
       <c r="C31" s="2" t="n"/>
       <c r="D31" s="2" t="n">
-        <v>39214000</v>
+        <v>11573000</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Toshkent Logistik MChJ</t>
+          <t>Zarafshon Poligraf MChJ</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>390251094</t>
+          <t>331756684</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>20208000862421413001</t>
+          <t>20208000798127163001</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №7664 за поставленный товар</t>
+          <t>ПРЕДОПЛАТА ЗА ТОВАР ПО ДОГОВОРУ №79/26 ОТ 15.07.2026</t>
         </is>
       </c>
       <c r="J31" s="2" t="n">
-        <v>183434000</v>
+        <v>412790000</v>
       </c>
     </row>
     <row r="32">
@@ -1492,301 +1492,301 @@
       </c>
       <c r="C32" s="2" t="n"/>
       <c r="D32" s="2" t="n">
-        <v>31850000</v>
+        <v>10330000</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Bahor Meva Eksport MChJ</t>
+          <t>Navro'z Agro MChJ</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>207825049</t>
+          <t>256816338</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>20208000822969351001</t>
+          <t>20208000624445379001</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>Оплата по с/ф №9379 за поставленный товар</t>
+          <t>Оплата за товар по счет-фактуре №1256 от 15.07.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J32" s="2" t="n">
-        <v>215284000</v>
+        <v>423120000</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="B33" t="n">
         <v>125</v>
       </c>
       <c r="C33" s="2" t="n"/>
       <c r="D33" s="2" t="n">
-        <v>21660000</v>
+        <v>10238000</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Nihol Qurilish Materiallari MChJ</t>
+          <t>Zarafshon Poligraf MChJ</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>246317566</t>
+          <t>331756684</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>20208000447981271001</t>
+          <t>20208000798127163001</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>Shartnoma №197/26 bo'yicha oldindan to'lov</t>
+          <t>Оплата за продукцию по договору №203/26, НДС 12%</t>
         </is>
       </c>
       <c r="J33" s="2" t="n">
-        <v>236944000</v>
+        <v>433358000</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="B34" t="n">
         <v>126</v>
       </c>
-      <c r="C34" s="2" t="n"/>
-      <c r="D34" s="2" t="n">
-        <v>11192000</v>
-      </c>
+      <c r="C34" s="2" t="n">
+        <v>15328000</v>
+      </c>
+      <c r="D34" s="2" t="n"/>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Qarshi Qurilish Materiallari MChJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>398397122</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>20208000732654438001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №121/26 от 15.07.2026</t>
+          <t>СОЦИАЛЬНЫЙ НАЛОГ ЗА ИЮНЬ 2026 Г.</t>
         </is>
       </c>
       <c r="J34" s="2" t="n">
-        <v>248136000</v>
+        <v>418030000</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="B35" t="n">
         <v>127</v>
       </c>
       <c r="C35" s="2" t="n">
-        <v>17552000</v>
+        <v>15328000</v>
       </c>
       <c r="D35" s="2" t="n"/>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Oydin Plastik MChJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>276196667</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>20208000603938553001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>Xom ashyo uchun to'lov, shartnoma №172/26, QQS bilan</t>
+          <t>НДФЛ ЗА ИЮНЬ 2026</t>
         </is>
       </c>
       <c r="J35" s="2" t="n">
-        <v>230584000</v>
+        <v>402702000</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="B36" t="n">
         <v>128</v>
       </c>
-      <c r="C36" s="2" t="n">
-        <v>15328000</v>
-      </c>
-      <c r="D36" s="2" t="n"/>
+      <c r="C36" s="2" t="n"/>
+      <c r="D36" s="2" t="n">
+        <v>30478000</v>
+      </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Zarafshon Poligraf MChJ</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>331756684</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000798127163001</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>Iyun oyi uchun ijtimoiy soliq</t>
+          <t>Оплата по счет-фактуре №2127 за поставленный товар</t>
         </is>
       </c>
       <c r="J36" s="2" t="n">
-        <v>215256000</v>
+        <v>433180000</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="n">
-        <v>46219</v>
+        <v>46223</v>
       </c>
       <c r="B37" t="n">
         <v>129</v>
       </c>
-      <c r="C37" s="2" t="n">
-        <v>15328000</v>
-      </c>
-      <c r="D37" s="2" t="n"/>
+      <c r="C37" s="2" t="n"/>
+      <c r="D37" s="2" t="n">
+        <v>47990000</v>
+      </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Zarafshon Poligraf MChJ</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>331756684</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000798127163001</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>Jismoniy shaxslar daromad solig'i iyun 2026</t>
+          <t>Оплата по счет-фактуре №823 за поставленный товар</t>
         </is>
       </c>
       <c r="J37" s="2" t="n">
-        <v>199928000</v>
+        <v>481170000</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="n">
-        <v>46220</v>
+        <v>46223</v>
       </c>
       <c r="B38" t="n">
         <v>130</v>
       </c>
-      <c r="C38" s="2" t="n">
-        <v>63725000</v>
-      </c>
-      <c r="D38" s="2" t="n"/>
+      <c r="C38" s="2" t="n"/>
+      <c r="D38" s="2" t="n">
+        <v>40856000</v>
+      </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Gulshan Poligraf MChJ</t>
+          <t>Navro'z Agro MChJ</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>321061342</t>
+          <t>256816338</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>20208000490421029001</t>
+          <t>20208000624445379001</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>Transport xizmatlari uchun to'lov, shartnoma №236/26</t>
+          <t>Mahsulot uchun to'lov, shartnoma №286/26, QQS 12%</t>
         </is>
       </c>
       <c r="J38" s="2" t="n">
-        <v>136203000</v>
+        <v>522026000</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="n">
-        <v>46220</v>
+        <v>46223</v>
       </c>
       <c r="B39" t="n">
         <v>131</v>
       </c>
-      <c r="C39" s="2" t="n">
-        <v>75388000</v>
-      </c>
-      <c r="D39" s="2" t="n"/>
+      <c r="C39" s="2" t="n"/>
+      <c r="D39" s="2" t="n">
+        <v>36714000</v>
+      </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Gulshan Poligraf MChJ</t>
+          <t>Zarafshon Poligraf MChJ</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>321061342</t>
+          <t>331756684</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>20208000490421029001</t>
+          <t>20208000798127163001</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -1796,11 +1796,11 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>Materiallar uchun oldindan to'lov, shartnoma №234/26</t>
+          <t>Tovar uchun to'lov, h/f №1579 20.07.2026, QQS bilan</t>
         </is>
       </c>
       <c r="J39" s="2" t="n">
-        <v>60815000</v>
+        <v>558740000</v>
       </c>
     </row>
     <row r="40">
@@ -1812,35 +1812,35 @@
       </c>
       <c r="C40" s="2" t="n"/>
       <c r="D40" s="2" t="n">
-        <v>29579000</v>
+        <v>19322000</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Nihol Qurilish Materiallari MChJ</t>
+          <t>Sharq Savdo MChJ</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>246317566</t>
+          <t>382504948</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>20208000447981271001</t>
+          <t>20208000296935100001</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №153/26, QQS 12%</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №6036</t>
         </is>
       </c>
       <c r="J40" s="2" t="n">
-        <v>90394000</v>
+        <v>578062000</v>
       </c>
     </row>
     <row r="41">
@@ -1852,35 +1852,35 @@
       </c>
       <c r="C41" s="2" t="n"/>
       <c r="D41" s="2" t="n">
-        <v>8835000</v>
+        <v>14755000</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Nihol Qurilish Materiallari MChJ</t>
+          <t>Zarafshon Poligraf MChJ</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>246317566</t>
+          <t>331756684</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>20208000447981271001</t>
+          <t>20208000798127163001</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №3610 20.07.2026, QQS bilan</t>
+          <t>Оплата за продукцию по договору №193/26, НДС 12%</t>
         </is>
       </c>
       <c r="J41" s="2" t="n">
-        <v>99229000</v>
+        <v>592817000</v>
       </c>
     </row>
     <row r="42">
@@ -1890,117 +1890,117 @@
       <c r="B42" t="n">
         <v>134</v>
       </c>
-      <c r="C42" s="2" t="n">
-        <v>25571000</v>
-      </c>
-      <c r="D42" s="2" t="n"/>
+      <c r="C42" s="2" t="n"/>
+      <c r="D42" s="2" t="n">
+        <v>9625000</v>
+      </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Yulduz Yog' Zavodi MChJ</t>
+          <t>Sarbon Mebel XK</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>259617057</t>
+          <t>202761813</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>20208000782301269001</t>
+          <t>20208000539456465001</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>Xom ashyo uchun to'lov, shartnoma №228/26, QQS bilan</t>
+          <t>Оплата по счет-фактуре №5963 за поставленный товар</t>
         </is>
       </c>
       <c r="J42" s="2" t="n">
-        <v>73658000</v>
+        <v>602442000</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="n">
-        <v>46224</v>
+        <v>46223</v>
       </c>
       <c r="B43" t="n">
         <v>135</v>
       </c>
-      <c r="C43" s="2" t="n"/>
-      <c r="D43" s="2" t="n">
-        <v>16000000</v>
-      </c>
+      <c r="C43" s="2" t="n">
+        <v>27608000</v>
+      </c>
+      <c r="D43" s="2" t="n"/>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Saodat Meva-Sabzavot MChJ</t>
+          <t>Farg'ona Metall Servis MChJ</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>352568163</t>
+          <t>244700213</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>20208000856244453001</t>
+          <t>20208000483988736001</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №1070</t>
+          <t>Оплата за транспортные услуги по договору №15/26</t>
         </is>
       </c>
       <c r="J43" s="2" t="n">
-        <v>89658000</v>
+        <v>574834000</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="n">
-        <v>46224</v>
+        <v>46223</v>
       </c>
       <c r="B44" t="n">
         <v>136</v>
       </c>
       <c r="C44" s="2" t="n">
-        <v>40209000</v>
+        <v>304414000</v>
       </c>
       <c r="D44" s="2" t="n"/>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Yulduz Yog' Zavodi MChJ</t>
+          <t>Farg'ona Metall Servis MChJ</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>259617057</t>
+          <t>244700213</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>20208000782301269001</t>
+          <t>20208000483988736001</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>Materiallar uchun oldindan to'lov, shartnoma №68/26</t>
+          <t>Предоплата за материалы по договору №192/26</t>
         </is>
       </c>
       <c r="J44" s="2" t="n">
-        <v>49449000</v>
+        <v>270420000</v>
       </c>
     </row>
     <row r="45">
@@ -2012,75 +2012,75 @@
       </c>
       <c r="C45" s="2" t="n"/>
       <c r="D45" s="2" t="n">
-        <v>21532000</v>
+        <v>175202000</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Nihol Qurilish Materiallari MChJ</t>
+          <t>Zarafshon Poligraf MChJ</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>246317566</t>
+          <t>331756684</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>20208000447981271001</t>
+          <t>20208000798127163001</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>Shartnoma №60/26 bo'yicha oldindan to'lov</t>
+          <t>Оплата по счет-фактуре №2009 за поставленный товар</t>
         </is>
       </c>
       <c r="J45" s="2" t="n">
-        <v>70981000</v>
+        <v>445622000</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="n">
-        <v>46226</v>
+        <v>46225</v>
       </c>
       <c r="B46" t="n">
         <v>138</v>
       </c>
-      <c r="C46" s="2" t="n"/>
-      <c r="D46" s="2" t="n">
-        <v>33385000</v>
-      </c>
+      <c r="C46" s="2" t="n">
+        <v>14833000</v>
+      </c>
+      <c r="D46" s="2" t="n"/>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Nihol Qurilish Materiallari MChJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>246317566</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>20208000447981271001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №5254 за пставленный товар</t>
+          <t>НДС за июнь 2026 г.</t>
         </is>
       </c>
       <c r="J46" s="2" t="n">
-        <v>104366000</v>
+        <v>430789000</v>
       </c>
     </row>
     <row r="47">
@@ -2090,77 +2090,77 @@
       <c r="B47" t="n">
         <v>139</v>
       </c>
-      <c r="C47" s="2" t="n">
-        <v>15006000</v>
-      </c>
-      <c r="D47" s="2" t="n"/>
+      <c r="C47" s="2" t="n"/>
+      <c r="D47" s="2" t="n">
+        <v>38977000</v>
+      </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Zarafshon Poligraf MChJ</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>331756684</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000798127163001</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>Qo'shilgan qiymat solig'i iyun oyi</t>
+          <t>Оплата за продукцию по договору №105/26, НДС 12%</t>
         </is>
       </c>
       <c r="J47" s="2" t="n">
-        <v>89360000</v>
+        <v>469766000</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="n">
-        <v>46227</v>
+        <v>46226</v>
       </c>
       <c r="B48" t="n">
         <v>140</v>
       </c>
       <c r="C48" s="2" t="n"/>
       <c r="D48" s="2" t="n">
-        <v>59616000</v>
+        <v>19079000</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Nihol Yog'och MChJ</t>
+          <t>Zarafshon Poligraf MChJ</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>216503395</t>
+          <t>331756684</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>20208000488704236001</t>
+          <t>20208000798127163001</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №3284</t>
+          <t>Оплата за товар по с/ф №9689 от 23.07.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J48" s="2" t="n">
-        <v>148976000</v>
+        <v>488845000</v>
       </c>
     </row>
     <row r="49">
@@ -2172,35 +2172,35 @@
       </c>
       <c r="C49" s="2" t="n"/>
       <c r="D49" s="2" t="n">
-        <v>19102000</v>
+        <v>87645000</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Nihol Qurilish Materiallari MChJ</t>
+          <t>Zarafshon Poligraf MChJ</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>246317566</t>
+          <t>331756684</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>20208000447981271001</t>
+          <t>20208000798127163001</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>TOVAR UCHUN TO'LOV, H/F №467 24.07.2026, QQS BILAN</t>
+          <t>Оплата за товар по счет-фактуре №2401 от 24.07.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J49" s="2" t="n">
-        <v>168078000</v>
+        <v>576490000</v>
       </c>
     </row>
     <row r="50">
@@ -2211,76 +2211,76 @@
         <v>142</v>
       </c>
       <c r="C50" s="2" t="n">
-        <v>51146000</v>
+        <v>5585000</v>
       </c>
       <c r="D50" s="2" t="n"/>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Gulshan Poligraf MChJ</t>
+          <t>Hududiy elektr tarmoqlari AJ</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>321061342</t>
+          <t>200933985</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>20208000490421029001</t>
+          <t>20208000977272336001</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>Tovarlar uchun to'lov h/f №9064</t>
+          <t>Оплата за электроэнергию согласно счету</t>
         </is>
       </c>
       <c r="J50" s="2" t="n">
-        <v>116932000</v>
+        <v>570905000</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="n">
-        <v>46230</v>
+        <v>46227</v>
       </c>
       <c r="B51" t="n">
         <v>143</v>
       </c>
-      <c r="C51" s="2" t="n"/>
-      <c r="D51" s="2" t="n">
-        <v>68213000</v>
-      </c>
+      <c r="C51" s="2" t="n">
+        <v>384522000</v>
+      </c>
+      <c r="D51" s="2" t="n"/>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Saodat Meva-Sabzavot MChJ</t>
+          <t>Farg'ona Metall Servis MChJ</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>352568163</t>
+          <t>244700213</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>20208000856244453001</t>
+          <t>20208000483988736001</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №5705 27.07.2026, QQS bilan</t>
+          <t>Оплата за упаковочные материалы, с/ф №7553</t>
         </is>
       </c>
       <c r="J51" s="2" t="n">
-        <v>185145000</v>
+        <v>186383000</v>
       </c>
     </row>
     <row r="52">
@@ -2292,35 +2292,35 @@
       </c>
       <c r="C52" s="2" t="n"/>
       <c r="D52" s="2" t="n">
-        <v>30000000</v>
+        <v>81542000</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Nihol Qurilish Materiallari MChJ</t>
+          <t>Navro'z Agro MChJ</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>246317566</t>
+          <t>256816338</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>20208000447981271001</t>
+          <t>20208000624445379001</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №5459</t>
+          <t>Оплата за товар по с/ф №832 от 27.07.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J52" s="2" t="n">
-        <v>215145000</v>
+        <v>267925000</v>
       </c>
     </row>
     <row r="53">
@@ -2332,35 +2332,35 @@
       </c>
       <c r="C53" s="2" t="n"/>
       <c r="D53" s="2" t="n">
-        <v>20791000</v>
+        <v>41238000</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Nihol Qurilish Materiallari MChJ</t>
+          <t>Qo'qon Mato MChJ</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>246317566</t>
+          <t>359614862</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>20208000447981271001</t>
+          <t>20208000130507081001</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №30/26, QQS 12%</t>
+          <t>Оплата за продукцию по договору №218/26, НДС 12%</t>
         </is>
       </c>
       <c r="J53" s="2" t="n">
-        <v>235936000</v>
+        <v>309163000</v>
       </c>
     </row>
     <row r="54">
@@ -2372,35 +2372,35 @@
       </c>
       <c r="C54" s="2" t="n"/>
       <c r="D54" s="2" t="n">
-        <v>9708000</v>
+        <v>20333000</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Nihol Qurilish Materiallari MChJ</t>
+          <t>Zarafshon Poligraf MChJ</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>246317566</t>
+          <t>331756684</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>20208000447981271001</t>
+          <t>20208000798127163001</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, h/f №9526 27.07.2026, QQS bilan</t>
+          <t>Оплата за продукцию по дог. №78/26, НДС 12%</t>
         </is>
       </c>
       <c r="J54" s="2" t="n">
-        <v>245644000</v>
+        <v>329496000</v>
       </c>
     </row>
     <row r="55">
@@ -2412,35 +2412,35 @@
       </c>
       <c r="C55" s="2" t="n"/>
       <c r="D55" s="2" t="n">
-        <v>7865000</v>
+        <v>13696000</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Nihol Qurilish Materiallari MChJ</t>
+          <t>Zarafshon Poligraf MChJ</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>246317566</t>
+          <t>331756684</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>20208000447981271001</t>
+          <t>20208000798127163001</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №9081</t>
+          <t>MAHSULOT UCHUN TO'LOV, SHARTN. №198/26, QQS 12%</t>
         </is>
       </c>
       <c r="J55" s="2" t="n">
-        <v>253509000</v>
+        <v>343192000</v>
       </c>
     </row>
     <row r="56">
@@ -2451,222 +2451,217 @@
         <v>148</v>
       </c>
       <c r="C56" s="2" t="n">
-        <v>5585000</v>
+        <v>20352000</v>
       </c>
       <c r="D56" s="2" t="n"/>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Hududiy elektr tarmoqlari AJ</t>
+          <t>Oqtosh Agro Servis MChJ</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>200933985</t>
+          <t>277163738</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>20208000322645921001</t>
+          <t>20208000017612936001</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>Elektr energiyasi uchun to'lov</t>
+          <t>Предоплата за материалы по договору №181/26</t>
         </is>
       </c>
       <c r="J56" s="2" t="n">
-        <v>247924000</v>
+        <v>322840000</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="n">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="B57" t="n">
         <v>149</v>
       </c>
-      <c r="C57" s="2" t="n">
-        <v>20255000</v>
-      </c>
-      <c r="D57" s="2" t="n"/>
+      <c r="C57" s="2" t="n"/>
+      <c r="D57" s="2" t="n">
+        <v>9138000</v>
+      </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Oydin Plastik MChJ</t>
+          <t>Sarbon Mebel XK</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>276196667</t>
+          <t>202761813</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>20208000603938553001</t>
+          <t>20208000539456465001</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>Tovarlar uchun to'lov h/f №8550</t>
+          <t>Оплата по с/ф №286 за поставленный товар</t>
         </is>
       </c>
       <c r="J57" s="2" t="n">
-        <v>227669000</v>
+        <v>331978000</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="n">
-        <v>46230</v>
+        <v>46232</v>
       </c>
       <c r="B58" t="n">
         <v>150</v>
       </c>
-      <c r="C58" s="2" t="n">
-        <v>35641000</v>
-      </c>
-      <c r="D58" s="2" t="n"/>
+      <c r="C58" s="2" t="n"/>
+      <c r="D58" s="2" t="n">
+        <v>26507000</v>
+      </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Andijon Tur Servis MChJ</t>
+          <t>Zarafshon Poligraf MChJ</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>303911698</t>
+          <t>331756684</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>20208000572864151001</t>
+          <t>20208000798127163001</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>Xom ashyo uchun to'lov, shartnoma №235/26, QQS bilan</t>
+          <t>Оплата за товар по счет-фактуре №2589 от 29.07.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J58" s="2" t="n">
-        <v>192028000</v>
+        <v>358485000</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="3" t="n">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="B59" t="n">
         <v>151</v>
       </c>
-      <c r="C59" s="2" t="n"/>
-      <c r="D59" s="2" t="n">
-        <v>33697000</v>
-      </c>
+      <c r="C59" s="2" t="n">
+        <v>19944000</v>
+      </c>
+      <c r="D59" s="2" t="n"/>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Chust Logistik MChJ</t>
+          <t>Oydin Mehmonxona AJ</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>284027618</t>
+          <t>339712267</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>20208000325394564001</t>
+          <t>20208000265443892001</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №7866</t>
+          <t>Оплата за товары согласно с/ф №6422</t>
         </is>
       </c>
       <c r="J59" s="2" t="n">
-        <v>225725000</v>
+        <v>338541000</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="n">
-        <v>46231</v>
+        <v>46233</v>
       </c>
       <c r="B60" t="n">
         <v>152</v>
       </c>
       <c r="C60" s="2" t="n"/>
       <c r="D60" s="2" t="n">
-        <v>8441000</v>
+        <v>26351000</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Chust Logistik MChJ</t>
+          <t>Sarbon Mebel XK</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>284027618</t>
+          <t>202761813</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>20208000325394564001</t>
+          <t>20208000539456465001</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun t'lov h/f №9584</t>
+          <t>Оплата за продукцию по дог. №188/26, НДС12%</t>
         </is>
       </c>
       <c r="J60" s="2" t="n">
-        <v>234166000</v>
+        <v>364892000</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="3" t="n">
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="B61" t="n">
         <v>153</v>
       </c>
-      <c r="C61" s="2" t="n"/>
-      <c r="D61" s="2" t="n">
-        <v>71617000</v>
-      </c>
+      <c r="C61" s="2" t="n">
+        <v>300000</v>
+      </c>
+      <c r="D61" s="2" t="n"/>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Saodat Meva-Sabzavot MChJ</t>
-        </is>
-      </c>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>352568163</t>
+          <t>Zarafshon Kredit Bank</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>20208000856244453001</t>
+          <t>45994000900000001001</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -2676,77 +2671,77 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №220/26, НДС 12%</t>
+          <t>Плата за SMS-информирование</t>
         </is>
       </c>
       <c r="J61" s="2" t="n">
-        <v>305783000</v>
+        <v>364592000</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="3" t="n">
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="B62" t="n">
         <v>154</v>
       </c>
-      <c r="C62" s="2" t="n"/>
-      <c r="D62" s="2" t="n">
-        <v>14797000</v>
-      </c>
+      <c r="C62" s="2" t="n">
+        <v>22327000</v>
+      </c>
+      <c r="D62" s="2" t="n"/>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Nihol Qurilish Materiallari MChJ</t>
+          <t>Oydin Mehmonxona AJ</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>246317566</t>
+          <t>339712267</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>20208000447981271001</t>
+          <t>20208000265443892001</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №9167</t>
+          <t>Оплата за транспортные услуги по договору №146/26</t>
         </is>
       </c>
       <c r="J62" s="2" t="n">
-        <v>320580000</v>
+        <v>342265000</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="3" t="n">
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="B63" t="n">
         <v>155</v>
       </c>
       <c r="C63" s="2" t="n">
-        <v>40428000</v>
+        <v>34517000</v>
       </c>
       <c r="D63" s="2" t="n"/>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Gulshan Poligraf MChJ</t>
+          <t>Oydin Mehmonxona AJ</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>321061342</t>
+          <t>339712267</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>20208000490421029001</t>
+          <t>20208000265443892001</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -2756,86 +2751,91 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>Оплата за сырье по договору №76/26 от 30.07.2026, НДС 12%</t>
+          <t>Предоплата за материалы по дог. №223/26</t>
         </is>
       </c>
       <c r="J63" s="2" t="n">
-        <v>280152000</v>
+        <v>307748000</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="3" t="n">
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="B64" t="n">
         <v>156</v>
       </c>
       <c r="C64" s="2" t="n"/>
       <c r="D64" s="2" t="n">
-        <v>24242000</v>
+        <v>518000</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Nihol Qurilish Materiallari MChJ</t>
+          <t>Navro'z Agro MChJ</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>246317566</t>
+          <t>256816338</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>20208000447981271001</t>
+          <t>20208000624445379001</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №8916 за поставленный товар</t>
+          <t>Предоплата за товар по дог. №169/26 от 03.08.2026</t>
         </is>
       </c>
       <c r="J64" s="2" t="n">
-        <v>304394000</v>
+        <v>308266000</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="3" t="n">
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="B65" t="n">
         <v>157</v>
       </c>
-      <c r="C65" s="2" t="n">
-        <v>300000</v>
-      </c>
-      <c r="D65" s="2" t="n"/>
+      <c r="C65" s="2" t="n"/>
+      <c r="D65" s="2" t="n">
+        <v>253000</v>
+      </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Zarafshon Kredit Bank</t>
+          <t>Qo'qon Mato MChJ</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>359614862</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>45994000900000001001</t>
+          <t>20208000130507081001</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>Hisob-kassa xizmati uchun haq</t>
+          <t>Оплата за товар по с/ф №4366 от 03.08.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J65" s="2" t="n">
-        <v>304094000</v>
+        <v>308519000</v>
       </c>
     </row>
     <row r="66">
@@ -2847,35 +2847,35 @@
       </c>
       <c r="C66" s="2" t="n"/>
       <c r="D66" s="2" t="n">
-        <v>234000</v>
+        <v>119000</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Qarshi Qurilish Materiallari MChJ</t>
+          <t>Zarafshon Poligraf MChJ</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>398397122</t>
+          <t>331756684</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>20208000732654438001</t>
+          <t>20208000798127163001</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №4049</t>
+          <t>Оплата за продукцию по дог. №230/26, НДС 12%</t>
         </is>
       </c>
       <c r="J66" s="2" t="n">
-        <v>304328000</v>
+        <v>308638000</v>
       </c>
     </row>
     <row r="67">
@@ -2887,21 +2887,21 @@
       </c>
       <c r="C67" s="2" t="n"/>
       <c r="D67" s="2" t="n">
-        <v>96000</v>
+        <v>78000</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Saodat Meva-Sabzavot MChJ</t>
+          <t>Zarafshon Poligraf MChJ</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>352568163</t>
+          <t>331756684</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>20208000856244453001</t>
+          <t>20208000798127163001</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -2911,11 +2911,11 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №39/26, QQS 12%</t>
+          <t>ОПЛАТА ПО СЧЕТ-ФАКТУРЕ №72 ЗА ПОСТАВЛЕННЫЙ ТОВАР</t>
         </is>
       </c>
       <c r="J67" s="2" t="n">
-        <v>304424000</v>
+        <v>308716000</v>
       </c>
     </row>
     <row r="68">
@@ -2927,35 +2927,35 @@
       </c>
       <c r="C68" s="2" t="n"/>
       <c r="D68" s="2" t="n">
-        <v>79000</v>
+        <v>66000</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Chust Logistik MChJ</t>
+          <t>Zarafshon Poligraf MChJ</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>284027618</t>
+          <t>331756684</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>20208000325394564001</t>
+          <t>20208000798127163001</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №221/26 от 03.08.2026</t>
+          <t>Предоплата за товар по дог. №294/26 от 03.08.2026</t>
         </is>
       </c>
       <c r="J68" s="2" t="n">
-        <v>304503000</v>
+        <v>308782000</v>
       </c>
     </row>
     <row r="69">
@@ -2967,35 +2967,35 @@
       </c>
       <c r="C69" s="2" t="n"/>
       <c r="D69" s="2" t="n">
-        <v>68000</v>
+        <v>59000</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Saodat Meva-Sabzavot MChJ</t>
+          <t>Navro'z Agro MChJ</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>352568163</t>
+          <t>256816338</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>20208000856244453001</t>
+          <t>20208000624445379001</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №5909</t>
+          <t>Tovar uchun to'lov, hisob-faktura №857 03.08.2026, QQS bilan</t>
         </is>
       </c>
       <c r="J69" s="2" t="n">
-        <v>304571000</v>
+        <v>308841000</v>
       </c>
     </row>
     <row r="70">
@@ -3006,22 +3006,22 @@
         <v>162</v>
       </c>
       <c r="C70" s="2" t="n">
-        <v>19545000</v>
+        <v>19673000</v>
       </c>
       <c r="D70" s="2" t="n"/>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Gulshan Poligraf MChJ</t>
+          <t>Oydin Mehmonxona AJ</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>321061342</t>
+          <t>339712267</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>20208000490421029001</t>
+          <t>20208000265443892001</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -3031,37 +3031,37 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>Transport xizmatlari uchun to'lov, shartnoma №299/26</t>
+          <t>Оплата за транспортные услуги по договору №71/26</t>
         </is>
       </c>
       <c r="J70" s="2" t="n">
-        <v>285026000</v>
+        <v>289168000</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="3" t="n">
-        <v>46238</v>
+        <v>46237</v>
       </c>
       <c r="B71" t="n">
         <v>163</v>
       </c>
       <c r="C71" s="2" t="n">
-        <v>65050000</v>
+        <v>124116000</v>
       </c>
       <c r="D71" s="2" t="n"/>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Gulshan Poligraf MChJ</t>
+          <t>Oydin Mehmonxona AJ</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>321061342</t>
+          <t>339712267</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>20208000490421029001</t>
+          <t>20208000265443892001</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -3071,91 +3071,91 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>Transport xizmatlari uchun to'lov, shartn. №23/26</t>
+          <t>Tovarlar uchun to'lov h/f №7738</t>
         </is>
       </c>
       <c r="J71" s="2" t="n">
-        <v>219976000</v>
+        <v>165052000</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="3" t="n">
-        <v>46239</v>
+        <v>46238</v>
       </c>
       <c r="B72" t="n">
         <v>164</v>
       </c>
       <c r="C72" s="2" t="n"/>
       <c r="D72" s="2" t="n">
-        <v>216000</v>
+        <v>66000</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Nihol Qurilish Materiallari MChJ</t>
+          <t>Zarafshon Poligraf MChJ</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>246317566</t>
+          <t>331756684</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>20208000447981271001</t>
+          <t>20208000798127163001</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №827 от 05.08.2026, в т.ч. НДС 12%</t>
+          <t>Оплата по счет-фактуре №2408 за поставленный товар</t>
         </is>
       </c>
       <c r="J72" s="2" t="n">
-        <v>220192000</v>
+        <v>165118000</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="3" t="n">
-        <v>46239</v>
+        <v>46238</v>
       </c>
       <c r="B73" t="n">
         <v>165</v>
       </c>
-      <c r="C73" s="2" t="n"/>
-      <c r="D73" s="2" t="n">
-        <v>145000</v>
-      </c>
+      <c r="C73" s="2" t="n">
+        <v>100457000</v>
+      </c>
+      <c r="D73" s="2" t="n"/>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Nihol Qurilish Materiallari MChJ</t>
+          <t>Farg'ona Metall Servis MChJ</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>246317566</t>
+          <t>244700213</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>20208000447981271001</t>
+          <t>20208000483988736001</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №186/26 от 05.08.2026</t>
+          <t>Оплата за товары согласно счет-фактуре №3870</t>
         </is>
       </c>
       <c r="J73" s="2" t="n">
-        <v>220337000</v>
+        <v>64661000</v>
       </c>
     </row>
     <row r="74">
@@ -3167,35 +3167,35 @@
       </c>
       <c r="C74" s="2" t="n"/>
       <c r="D74" s="2" t="n">
-        <v>114000</v>
+        <v>658000</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Nihol Qurilish Materiallari MChJ</t>
+          <t>Zarafshon Poligraf MChJ</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>246317566</t>
+          <t>331756684</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>20208000447981271001</t>
+          <t>20208000798127163001</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №9686</t>
+          <t>Оплата по счет-фактуре №774 за поставленный товар</t>
         </is>
       </c>
       <c r="J74" s="2" t="n">
-        <v>220451000</v>
+        <v>65319000</v>
       </c>
     </row>
     <row r="75">
@@ -3230,47 +3230,42 @@
         </is>
       </c>
       <c r="J75" s="2" t="n">
-        <v>118051000</v>
+        <v>-37081000</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="3" t="n">
-        <v>46240</v>
+        <v>46239</v>
       </c>
       <c r="B76" t="n">
         <v>168</v>
       </c>
-      <c r="C76" s="2" t="n"/>
-      <c r="D76" s="2" t="n">
-        <v>149000</v>
-      </c>
+      <c r="C76" s="2" t="n">
+        <v>102604000</v>
+      </c>
+      <c r="D76" s="2" t="n"/>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Nihol Qurilish Materiallari MChJ</t>
-        </is>
-      </c>
-      <c r="F76" t="inlineStr">
-        <is>
-          <t>246317566</t>
+          <t>Zarafshon Kredit Bank</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>20208000447981271001</t>
+          <t>45994000900000001001</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №2208</t>
+          <t>Перечисление заработной платы за июль 2026 г. согласно реестру №5707</t>
         </is>
       </c>
       <c r="J76" s="2" t="n">
-        <v>118200000</v>
+        <v>-139685000</v>
       </c>
     </row>
     <row r="77">
@@ -3280,37 +3275,37 @@
       <c r="B77" t="n">
         <v>169</v>
       </c>
-      <c r="C77" s="2" t="n">
-        <v>49350000</v>
-      </c>
-      <c r="D77" s="2" t="n"/>
+      <c r="C77" s="2" t="n"/>
+      <c r="D77" s="2" t="n">
+        <v>586000</v>
+      </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Gulshan Poligraf MChJ</t>
+          <t>Sharq Savdo MChJ</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>321061342</t>
+          <t>382504948</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>20208000490421029001</t>
+          <t>20208000296935100001</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>Предопата за материалы по договору №170/26</t>
+          <t>Оплата по счет-фактуре №2168 за поставленный товар</t>
         </is>
       </c>
       <c r="J77" s="2" t="n">
-        <v>68850000</v>
+        <v>-139099000</v>
       </c>
     </row>
     <row r="78">
@@ -3320,18 +3315,23 @@
       <c r="B78" t="n">
         <v>170</v>
       </c>
-      <c r="C78" s="2" t="n">
-        <v>102604000</v>
-      </c>
-      <c r="D78" s="2" t="n"/>
+      <c r="C78" s="2" t="n"/>
+      <c r="D78" s="2" t="n">
+        <v>330000</v>
+      </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Zarafshon Kredit Bank</t>
+          <t>Zarafshon Poligraf MChJ</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>331756684</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>45994000900000001001</t>
+          <t>20208000798127163001</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -3341,51 +3341,51 @@
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>Ish haqi to'lovi iyul 2026 (plastik kartalarga)</t>
+          <t>Предоплата за товар по договору №241/26 от 06.08.2026</t>
         </is>
       </c>
       <c r="J78" s="2" t="n">
-        <v>-33754000</v>
+        <v>-138769000</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="3" t="n">
-        <v>46241</v>
+        <v>46240</v>
       </c>
       <c r="B79" t="n">
         <v>171</v>
       </c>
       <c r="C79" s="2" t="n"/>
       <c r="D79" s="2" t="n">
-        <v>214000</v>
+        <v>112000</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Nihol Qurilish Materiallari MChJ</t>
+          <t>Zarafshon Poligraf MChJ</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>246317566</t>
+          <t>331756684</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>20208000447981271001</t>
+          <t>20208000798127163001</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №224/26 от 07.08.2026</t>
+          <t>Оплата за продукцию по договору №61/26, НДС 12%</t>
         </is>
       </c>
       <c r="J79" s="2" t="n">
-        <v>-33540000</v>
+        <v>-138657000</v>
       </c>
     </row>
     <row r="80">
@@ -3401,22 +3401,22 @@
       <c r="D80" s="2" t="n"/>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Ilhom Qurilish Materiallari AJ</t>
+          <t>Shodlik Qurilish MChJ</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>372723361</t>
+          <t>354336802</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>20208000768964202001</t>
+          <t>20208000212400074001</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -3425,33 +3425,33 @@
         </is>
       </c>
       <c r="J80" s="2" t="n">
-        <v>-41697000</v>
+        <v>-146814000</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="3" t="n">
-        <v>46241</v>
+        <v>46244</v>
       </c>
       <c r="B81" t="n">
         <v>173</v>
       </c>
-      <c r="C81" s="2" t="n">
-        <v>175687000</v>
-      </c>
-      <c r="D81" s="2" t="n"/>
+      <c r="C81" s="2" t="n"/>
+      <c r="D81" s="2" t="n">
+        <v>764000</v>
+      </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Gulshan Poligraf MChJ</t>
+          <t>Zarafshon Poligraf MChJ</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>321061342</t>
+          <t>331756684</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>20208000490421029001</t>
+          <t>20208000798127163001</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -3461,11 +3461,11 @@
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>Xom ashyo uchun to'lov, shartnoma №112/26, QQS bilan</t>
+          <t>Оплата по с/ф №2956 за поставленный товар</t>
         </is>
       </c>
       <c r="J81" s="2" t="n">
-        <v>-217384000</v>
+        <v>-146050000</v>
       </c>
     </row>
     <row r="82">
@@ -3477,35 +3477,35 @@
       </c>
       <c r="C82" s="2" t="n"/>
       <c r="D82" s="2" t="n">
-        <v>373000</v>
+        <v>351000</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Nihol Qurilish Materiallari MChJ</t>
+          <t>Navro'z Agro MChJ</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>246317566</t>
+          <t>256816338</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>20208000447981271001</t>
+          <t>20208000624445379001</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №4394 10.08.2026, QQS bilan</t>
+          <t>Оплата за товар по счет-фактуре №6193 от 10.08.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J82" s="2" t="n">
-        <v>-217011000</v>
+        <v>-145699000</v>
       </c>
     </row>
     <row r="83">
@@ -3517,35 +3517,35 @@
       </c>
       <c r="C83" s="2" t="n"/>
       <c r="D83" s="2" t="n">
-        <v>301000</v>
+        <v>315000</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Chust Logistik MChJ</t>
+          <t>Navro'z Agro MChJ</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>284027618</t>
+          <t>256816338</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>20208000325394564001</t>
+          <t>20208000624445379001</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №1508 10.08.2026, QQS bilan</t>
+          <t>Оплата по счет-фактуре №8590 за поставленный товар</t>
         </is>
       </c>
       <c r="J83" s="2" t="n">
-        <v>-216710000</v>
+        <v>-145384000</v>
       </c>
     </row>
     <row r="84">
@@ -3557,35 +3557,35 @@
       </c>
       <c r="C84" s="2" t="n"/>
       <c r="D84" s="2" t="n">
-        <v>145000</v>
+        <v>292000</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Nihol Qurilish Materiallari MChJ</t>
+          <t>Navro'z Agro MChJ</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>246317566</t>
+          <t>256816338</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>20208000447981271001</t>
+          <t>20208000624445379001</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №187/26, QQS 12%</t>
+          <t>Предоплата за товар по договору №257/26 от 10.08.2026</t>
         </is>
       </c>
       <c r="J84" s="2" t="n">
-        <v>-216565000</v>
+        <v>-145092000</v>
       </c>
     </row>
     <row r="85">
@@ -3597,35 +3597,35 @@
       </c>
       <c r="C85" s="2" t="n"/>
       <c r="D85" s="2" t="n">
-        <v>71000</v>
+        <v>132000</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Nihol Qurilish Materiallari MChJ</t>
+          <t>Zarafshon Poligraf MChJ</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>246317566</t>
+          <t>331756684</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>20208000447981271001</t>
+          <t>20208000798127163001</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>Shartnoma №109/26 bo'yicha oldindan to'lov</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №3407</t>
         </is>
       </c>
       <c r="J85" s="2" t="n">
-        <v>-216494000</v>
+        <v>-144960000</v>
       </c>
     </row>
     <row r="86">
@@ -3635,317 +3635,317 @@
       <c r="B86" t="n">
         <v>178</v>
       </c>
-      <c r="C86" s="2" t="n"/>
-      <c r="D86" s="2" t="n">
-        <v>65000</v>
-      </c>
+      <c r="C86" s="2" t="n">
+        <v>30300000</v>
+      </c>
+      <c r="D86" s="2" t="n"/>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Nihol Qurilish Materiallari MChJ</t>
+          <t>Oydin Plastik XK</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>246317566</t>
+          <t>319666756</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>20208000447981271001</t>
+          <t>20208000393855383001</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №6619 10.08.2026, QS bilan</t>
+          <t>Оплата за сырье по договору №162/26 от 10.08.2026, НДС 12%</t>
         </is>
       </c>
       <c r="J86" s="2" t="n">
-        <v>-216429000</v>
+        <v>-175260000</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="3" t="n">
-        <v>46246</v>
+        <v>46245</v>
       </c>
       <c r="B87" t="n">
         <v>179</v>
       </c>
-      <c r="C87" s="2" t="n">
-        <v>83318000</v>
-      </c>
-      <c r="D87" s="2" t="n"/>
+      <c r="C87" s="2" t="n"/>
+      <c r="D87" s="2" t="n">
+        <v>192000</v>
+      </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Gulshan Poligraf MChJ</t>
+          <t>Sarbon Mebel XK</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>321061342</t>
+          <t>202761813</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>20208000490421029001</t>
+          <t>20208000539456465001</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>Оплата за упаковочные материалы, с/ф №6389</t>
+          <t>Mahsulot uchun to'lov, shartnoma №237/26, QQS 12%</t>
         </is>
       </c>
       <c r="J87" s="2" t="n">
-        <v>-299747000</v>
+        <v>-175068000</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="3" t="n">
-        <v>46246</v>
+        <v>46245</v>
       </c>
       <c r="B88" t="n">
         <v>180</v>
       </c>
       <c r="C88" s="2" t="n">
-        <v>175808000</v>
+        <v>42723000</v>
       </c>
       <c r="D88" s="2" t="n"/>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Namangan Savdo MChJ</t>
+          <t>Oydin Plastik XK</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>285433680</t>
+          <t>319666756</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>20208000021240007001</t>
+          <t>20208000393855383001</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>Tovarlar uchun to'lov h/f №3978</t>
+          <t>Оплата за товары согласно счет-фактуре №7192</t>
         </is>
       </c>
       <c r="J88" s="2" t="n">
-        <v>-475555000</v>
+        <v>-217791000</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="3" t="n">
-        <v>46247</v>
+        <v>46246</v>
       </c>
       <c r="B89" t="n">
         <v>181</v>
       </c>
       <c r="C89" s="2" t="n"/>
       <c r="D89" s="2" t="n">
-        <v>281000</v>
+        <v>208000</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Nihol Qurilish Materiallari MChJ</t>
+          <t>Navro'z Agro MChJ</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>246317566</t>
+          <t>256816338</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>20208000447981271001</t>
+          <t>20208000624445379001</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>Shartnoma №291/26 bo'yicha oldindan to'lov</t>
+          <t>Оплата за продукцию по договору №291/26, НДС 12%</t>
         </is>
       </c>
       <c r="J89" s="2" t="n">
-        <v>-475274000</v>
+        <v>-217583000</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="3" t="n">
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="B90" t="n">
         <v>182</v>
       </c>
       <c r="C90" s="2" t="n"/>
       <c r="D90" s="2" t="n">
-        <v>98000</v>
+        <v>69000</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Qarshi Qurilish Materiallari MChJ</t>
+          <t>Sharq Savdo MChJ</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>398397122</t>
+          <t>382504948</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>20208000732654438001</t>
+          <t>20208000296935100001</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>Shartnoma №35/26 bo'yicha oldindan to'lov</t>
+          <t>Shartnoma №252/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
       <c r="J90" s="2" t="n">
-        <v>-475176000</v>
+        <v>-217514000</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="3" t="n">
-        <v>46247</v>
+        <v>46251</v>
       </c>
       <c r="B91" t="n">
         <v>183</v>
       </c>
       <c r="C91" s="2" t="n"/>
       <c r="D91" s="2" t="n">
-        <v>75000</v>
+        <v>372000</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Nihol Qurilish Materiallari MChJ</t>
+          <t>Zarafshon Poligraf MChJ</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>246317566</t>
+          <t>331756684</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>20208000447981271001</t>
+          <t>20208000798127163001</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>Shartnoma №182/26 bo'yicha oldindan to'lov</t>
+          <t>Оплата за продукцию по договору №243/26, НДС 12%</t>
         </is>
       </c>
       <c r="J91" s="2" t="n">
-        <v>-475101000</v>
+        <v>-217142000</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="3" t="n">
-        <v>46248</v>
+        <v>46251</v>
       </c>
       <c r="B92" t="n">
         <v>184</v>
       </c>
       <c r="C92" s="2" t="n"/>
       <c r="D92" s="2" t="n">
-        <v>259000</v>
+        <v>223000</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Saodat Meva-Sabzavot MChJ</t>
+          <t>Navro'z Agro MChJ</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>352568163</t>
+          <t>256816338</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>20208000856244453001</t>
+          <t>20208000624445379001</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'ov, shartn. №3/26, QQS 12%</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №2159</t>
         </is>
       </c>
       <c r="J92" s="2" t="n">
-        <v>-474842000</v>
+        <v>-216919000</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="3" t="n">
-        <v>46248</v>
+        <v>46251</v>
       </c>
       <c r="B93" t="n">
         <v>185</v>
       </c>
       <c r="C93" s="2" t="n"/>
       <c r="D93" s="2" t="n">
-        <v>61000</v>
+        <v>213000</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Chust Logistik MChJ</t>
+          <t>Zarafshon Poligraf MChJ</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>284027618</t>
+          <t>331756684</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>20208000325394564001</t>
+          <t>20208000798127163001</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №3557</t>
+          <t>Оплата по счет-фактуре №1983 за поставленный товар</t>
         </is>
       </c>
       <c r="J93" s="2" t="n">
-        <v>-474781000</v>
+        <v>-216706000</v>
       </c>
     </row>
     <row r="94">
@@ -3957,35 +3957,35 @@
       </c>
       <c r="C94" s="2" t="n"/>
       <c r="D94" s="2" t="n">
-        <v>603000</v>
+        <v>178000</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Nihol Qurilish Materiallari MChJ</t>
+          <t>Sarbon Mebel XK</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>246317566</t>
+          <t>202761813</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>20208000447981271001</t>
+          <t>20208000539456465001</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №7839 за поставленный товар</t>
+          <t>Предоплата за товар по дог. №57/26 от 17.08.2026</t>
         </is>
       </c>
       <c r="J94" s="2" t="n">
-        <v>-474178000</v>
+        <v>-216528000</v>
       </c>
     </row>
     <row r="95">
@@ -3997,35 +3997,35 @@
       </c>
       <c r="C95" s="2" t="n"/>
       <c r="D95" s="2" t="n">
-        <v>87000</v>
+        <v>113000</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Nihol Qurilish Materiallari MChJ</t>
+          <t>Zarafshon Poligraf MChJ</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>246317566</t>
+          <t>331756684</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>20208000447981271001</t>
+          <t>20208000798127163001</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>Shartnoma №282/26 bo'yicha oldindan to'lov</t>
+          <t>Shartnoma №19/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
       <c r="J95" s="2" t="n">
-        <v>-474091000</v>
+        <v>-216415000</v>
       </c>
     </row>
     <row r="96">
@@ -4035,37 +4035,37 @@
       <c r="B96" t="n">
         <v>188</v>
       </c>
-      <c r="C96" s="2" t="n">
-        <v>13991000</v>
-      </c>
-      <c r="D96" s="2" t="n"/>
+      <c r="C96" s="2" t="n"/>
+      <c r="D96" s="2" t="n">
+        <v>83000</v>
+      </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Qo'qon Mato MChJ</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>359614862</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000130507081001</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>Iyul oyi uchun ijtimoiy soliq</t>
+          <t>ОПЛАТА ЗА ПРОДУКЦИЮ ПО ДОГ. №94/26, НДС 12%</t>
         </is>
       </c>
       <c r="J96" s="2" t="n">
-        <v>-488082000</v>
+        <v>-216332000</v>
       </c>
     </row>
     <row r="97">
@@ -4101,11 +4101,11 @@
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>JShDS iyul oyi uchun</t>
+          <t>Социальный налог за июль 2026 г.</t>
         </is>
       </c>
       <c r="J97" s="2" t="n">
-        <v>-502073000</v>
+        <v>-230323000</v>
       </c>
     </row>
     <row r="98">
@@ -4116,62 +4116,62 @@
         <v>190</v>
       </c>
       <c r="C98" s="2" t="n">
-        <v>53869000</v>
+        <v>13991000</v>
       </c>
       <c r="D98" s="2" t="n"/>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Gulshan Poligraf MChJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>321061342</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>20208000490421029001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>TRANSPORT XIZMATLARI UCHUN TO'LOV, SHARTNOMA №188/26</t>
+          <t>НДФЛ за июль 2026</t>
         </is>
       </c>
       <c r="J98" s="2" t="n">
-        <v>-555942000</v>
+        <v>-244314000</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="3" t="n">
-        <v>46253</v>
+        <v>46252</v>
       </c>
       <c r="B99" t="n">
         <v>191</v>
       </c>
       <c r="C99" s="2" t="n"/>
       <c r="D99" s="2" t="n">
-        <v>1121250000</v>
+        <v>129000</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Oltin Vodiy Mebel MChJ</t>
+          <t>Zarafshon Poligraf MChJ</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>297197550</t>
+          <t>331756684</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>20208000006090507001</t>
+          <t>20208000798127163001</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -4181,371 +4181,371 @@
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №52/26, QQS 12%</t>
+          <t>ОПЛАТА ПО СЧЕТ-ФАКТУРЕ №8805 ЗА ПОСТАВЛЕННЫЙ ТОВАР</t>
         </is>
       </c>
       <c r="J99" s="2" t="n">
-        <v>565308000</v>
+        <v>-244185000</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="3" t="n">
-        <v>46253</v>
+        <v>46252</v>
       </c>
       <c r="B100" t="n">
         <v>192</v>
       </c>
       <c r="C100" s="2" t="n"/>
       <c r="D100" s="2" t="n">
-        <v>509000</v>
+        <v>103000</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Nihol Qurilish Materiallari MChJ</t>
+          <t>Navro'z Agro MChJ</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>246317566</t>
+          <t>256816338</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>20208000447981271001</t>
+          <t>20208000624445379001</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, h/f №9319 19.08.2026, QQS bilan</t>
+          <t>Оплата за товар по с/ф №7285 от 18.08.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J100" s="2" t="n">
-        <v>565817000</v>
+        <v>-244082000</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="3" t="n">
-        <v>46253</v>
+        <v>46252</v>
       </c>
       <c r="B101" t="n">
         <v>193</v>
       </c>
-      <c r="C101" s="2" t="n"/>
-      <c r="D101" s="2" t="n">
-        <v>261000</v>
-      </c>
+      <c r="C101" s="2" t="n">
+        <v>26224000</v>
+      </c>
+      <c r="D101" s="2" t="n"/>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Nihol Qurilish Materiallari MChJ</t>
+          <t>Oydin Mehmonxona AJ</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>246317566</t>
+          <t>339712267</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>20208000447981271001</t>
+          <t>20208000265443892001</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>Shartnoma №298/26 bo'yicha oldindan to'lov</t>
+          <t>Оплат за упаковочные материалы, с/ф №41</t>
         </is>
       </c>
       <c r="J101" s="2" t="n">
-        <v>566078000</v>
+        <v>-270306000</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="3" t="n">
-        <v>46254</v>
+        <v>46253</v>
       </c>
       <c r="B102" t="n">
         <v>194</v>
       </c>
       <c r="C102" s="2" t="n"/>
       <c r="D102" s="2" t="n">
-        <v>342000</v>
+        <v>273000</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Xiva Sut AJ</t>
+          <t>Zarafshon Poligraf MChJ</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>259596148</t>
+          <t>331756684</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>20208000211305070001</t>
+          <t>20208000798127163001</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>Shartnoma №81/26 bo'yicha oldindan to'lov</t>
+          <t>Оплата за продукцию по договору №242/26, НДС 12%</t>
         </is>
       </c>
       <c r="J102" s="2" t="n">
-        <v>566420000</v>
+        <v>-270033000</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="3" t="n">
-        <v>46255</v>
+        <v>46254</v>
       </c>
       <c r="B103" t="n">
         <v>195</v>
       </c>
       <c r="C103" s="2" t="n"/>
       <c r="D103" s="2" t="n">
-        <v>383000</v>
+        <v>252000</v>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Nihol Qurilish Materiallari MChJ</t>
+          <t>Navro'z Agro MChJ</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>246317566</t>
+          <t>256816338</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>20208000447981271001</t>
+          <t>20208000624445379001</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по дог. №269/26, НДС 12%</t>
+          <t>Оплата по счет-фактуре №8667 за поставленный товар</t>
         </is>
       </c>
       <c r="J103" s="2" t="n">
-        <v>566803000</v>
+        <v>-269781000</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="3" t="n">
-        <v>46255</v>
+        <v>46254</v>
       </c>
       <c r="B104" t="n">
         <v>196</v>
       </c>
-      <c r="C104" s="2" t="n">
-        <v>13557000</v>
-      </c>
-      <c r="D104" s="2" t="n"/>
+      <c r="C104" s="2" t="n"/>
+      <c r="D104" s="2" t="n">
+        <v>158000</v>
+      </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Navro'z Agro MChJ</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>256816338</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000624445379001</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>Qo'shilgan qiymat solig'i iyul oyi</t>
+          <t>Оплата по счет-фактуре №5231 за поставленный товар</t>
         </is>
       </c>
       <c r="J104" s="2" t="n">
-        <v>553246000</v>
+        <v>-269623000</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="3" t="n">
-        <v>46255</v>
+        <v>46254</v>
       </c>
       <c r="B105" t="n">
         <v>197</v>
       </c>
-      <c r="C105" s="2" t="n">
-        <v>28440000</v>
-      </c>
-      <c r="D105" s="2" t="n"/>
+      <c r="C105" s="2" t="n"/>
+      <c r="D105" s="2" t="n">
+        <v>56000</v>
+      </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Oydin Plastik MChJ</t>
+          <t>Zarafshon Poligraf MChJ</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>276196667</t>
+          <t>331756684</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>20208000603938553001</t>
+          <t>20208000798127163001</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>Materiallar uchun oldindan to'lov, shartn. №15/26</t>
+          <t>Предоплата за товар по дог. №171/26 от 20.08.2026</t>
         </is>
       </c>
       <c r="J105" s="2" t="n">
-        <v>524806000</v>
+        <v>-269567000</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="3" t="n">
-        <v>46258</v>
+        <v>46254</v>
       </c>
       <c r="B106" t="n">
         <v>198</v>
       </c>
-      <c r="C106" s="2" t="n"/>
-      <c r="D106" s="2" t="n">
-        <v>491000</v>
-      </c>
+      <c r="C106" s="2" t="n">
+        <v>227160000</v>
+      </c>
+      <c r="D106" s="2" t="n"/>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Toshkent Logistik MChJ</t>
+          <t>Oydin Mehmonxona AJ</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>390251094</t>
+          <t>339712267</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>20208000862421413001</t>
+          <t>20208000265443892001</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №3045</t>
+          <t>Оплата за сырье по договору №70/26 от 20.08.2026, НДС 12%</t>
         </is>
       </c>
       <c r="J106" s="2" t="n">
-        <v>525297000</v>
+        <v>-496727000</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="3" t="n">
-        <v>46258</v>
+        <v>46255</v>
       </c>
       <c r="B107" t="n">
         <v>199</v>
       </c>
-      <c r="C107" s="2" t="n"/>
-      <c r="D107" s="2" t="n">
-        <v>477000</v>
-      </c>
+      <c r="C107" s="2" t="n">
+        <v>13205000</v>
+      </c>
+      <c r="D107" s="2" t="n"/>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Chust Logistik MChJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>284027618</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>20208000325394564001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №97/26, QQS 12%</t>
+          <t>Уплата налога на добавленную стоимость за июль</t>
         </is>
       </c>
       <c r="J107" s="2" t="n">
-        <v>525774000</v>
+        <v>-509932000</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="3" t="n">
-        <v>46258</v>
+        <v>46255</v>
       </c>
       <c r="B108" t="n">
         <v>200</v>
       </c>
-      <c r="C108" s="2" t="n"/>
-      <c r="D108" s="2" t="n">
-        <v>162000</v>
-      </c>
+      <c r="C108" s="2" t="n">
+        <v>19594000</v>
+      </c>
+      <c r="D108" s="2" t="n"/>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Nihol Qurilish Materiallari MChJ</t>
+          <t>Navoiy Avto Ehtiyot MChJ</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>246317566</t>
+          <t>293875596</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>20208000447981271001</t>
+          <t>20208000589849151001</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartn. №258/26, QQS 12%</t>
+          <t>Оплата за транспортные услуги по договору №132/26</t>
         </is>
       </c>
       <c r="J108" s="2" t="n">
-        <v>525936000</v>
+        <v>-529526000</v>
       </c>
     </row>
     <row r="109">
@@ -4557,35 +4557,35 @@
       </c>
       <c r="C109" s="2" t="n"/>
       <c r="D109" s="2" t="n">
-        <v>106000</v>
+        <v>1089872000</v>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Mehnat Yog' Zavodi MChJ</t>
+          <t>Zarafshon Poligraf MChJ</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>250447002</t>
+          <t>331756684</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>20208000314839887001</t>
+          <t>20208000798127163001</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по дог. №3/26, НДС 12%</t>
+          <t>Оплата за продукцию по договору №122/26, НДС 12%</t>
         </is>
       </c>
       <c r="J109" s="2" t="n">
-        <v>526042000</v>
+        <v>560346000</v>
       </c>
     </row>
     <row r="110">
@@ -4597,21 +4597,21 @@
       </c>
       <c r="C110" s="2" t="n"/>
       <c r="D110" s="2" t="n">
-        <v>92000</v>
+        <v>228000</v>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Saodat Meva-Sabzavot MChJ</t>
+          <t>Zarafshon Poligraf MChJ</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>352568163</t>
+          <t>331756684</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>20208000856244453001</t>
+          <t>20208000798127163001</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
@@ -4621,11 +4621,11 @@
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, h/f №7250 24.08.2026, QQS bilan</t>
+          <t>Предоплата за товар по договору №180/26 от 24.08.2026</t>
         </is>
       </c>
       <c r="J110" s="2" t="n">
-        <v>526134000</v>
+        <v>560574000</v>
       </c>
     </row>
     <row r="111">
@@ -4637,35 +4637,35 @@
       </c>
       <c r="C111" s="2" t="n"/>
       <c r="D111" s="2" t="n">
-        <v>86000</v>
+        <v>215000</v>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Nihol Qurilish Materiallari MChJ</t>
+          <t>Zarafshon Poligraf MChJ</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>246317566</t>
+          <t>331756684</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>20208000447981271001</t>
+          <t>20208000798127163001</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №1439 24.08.2026, QQS bilan</t>
+          <t>Tovar uchun to'lov, hisob-faktura №3947 24.08.2026, QQS bilan</t>
         </is>
       </c>
       <c r="J111" s="2" t="n">
-        <v>526220000</v>
+        <v>560789000</v>
       </c>
     </row>
     <row r="112">
@@ -4677,35 +4677,35 @@
       </c>
       <c r="C112" s="2" t="n"/>
       <c r="D112" s="2" t="n">
-        <v>58000</v>
+        <v>210000</v>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Saodat Meva-Sabzavot MChJ</t>
+          <t>Navro'z Agro MChJ</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>352568163</t>
+          <t>256816338</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>20208000856244453001</t>
+          <t>20208000624445379001</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>SHARTNOMA №272/26 BO'YICHA OLDINDAN TO'LOV</t>
+          <t>Оплата за товар по счет-фактуре №3909 от 24.08.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J112" s="2" t="n">
-        <v>526278000</v>
+        <v>560999000</v>
       </c>
     </row>
     <row r="113">
@@ -4716,102 +4716,102 @@
         <v>205</v>
       </c>
       <c r="C113" s="2" t="n">
-        <v>5098000</v>
+        <v>25339000</v>
       </c>
       <c r="D113" s="2" t="n"/>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Hududiy elektr tarmoqlari AJ</t>
+          <t>Oydin Mehmonxona AJ</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>200933985</t>
+          <t>339712267</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>20208000322645921001</t>
+          <t>20208000265443892001</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>Elektr energiyasi uchun to'lov avgust</t>
+          <t>Оплата за сырье по договору №142/26 от 24.08.2026, НДС 12%</t>
         </is>
       </c>
       <c r="J113" s="2" t="n">
-        <v>521180000</v>
+        <v>535660000</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="3" t="n">
-        <v>46259</v>
+        <v>46258</v>
       </c>
       <c r="B114" t="n">
         <v>206</v>
       </c>
-      <c r="C114" s="2" t="n"/>
-      <c r="D114" s="2" t="n">
-        <v>361000</v>
-      </c>
+      <c r="C114" s="2" t="n">
+        <v>26042000</v>
+      </c>
+      <c r="D114" s="2" t="n"/>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Saodat Meva-Sabzavot MChJ</t>
+          <t>Yangi Hayot Sut Mahsulotlari MChJ</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>352568163</t>
+          <t>206134234</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>20208000856244453001</t>
+          <t>20208000042102996001</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>Shartnoma №190/26 bo'yicha oldindan to'lov</t>
+          <t>Оплата за транспортные услуги по договору №10/26</t>
         </is>
       </c>
       <c r="J114" s="2" t="n">
-        <v>521541000</v>
+        <v>509618000</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="3" t="n">
-        <v>46259</v>
+        <v>46258</v>
       </c>
       <c r="B115" t="n">
         <v>207</v>
       </c>
       <c r="C115" s="2" t="n">
-        <v>171045000</v>
+        <v>62097000</v>
       </c>
       <c r="D115" s="2" t="n"/>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Gulshan Poligraf MChJ</t>
+          <t>Oydin Mehmonxona AJ</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>321061342</t>
+          <t>339712267</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>20208000490421029001</t>
+          <t>20208000265443892001</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
@@ -4821,91 +4821,91 @@
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>Materiallar uchun oldindan to'lov, shartnoma №208/26</t>
+          <t>Оплата за товары согласно счет-фактуре №8406</t>
         </is>
       </c>
       <c r="J115" s="2" t="n">
-        <v>350496000</v>
+        <v>447521000</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="3" t="n">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="B116" t="n">
         <v>208</v>
       </c>
       <c r="C116" s="2" t="n"/>
       <c r="D116" s="2" t="n">
-        <v>232000</v>
+        <v>195000</v>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Nihol Qurilish Materiallari MChJ</t>
+          <t>Zarafshon Poligraf MChJ</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>246317566</t>
+          <t>331756684</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>20208000447981271001</t>
+          <t>20208000798127163001</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №70/26, QQS 12%</t>
+          <t>Оплата по счет-фактуре №3172 за поставленный товар</t>
         </is>
       </c>
       <c r="J116" s="2" t="n">
-        <v>350728000</v>
+        <v>447716000</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="3" t="n">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="B117" t="n">
         <v>209</v>
       </c>
-      <c r="C117" s="2" t="n">
-        <v>18521000</v>
-      </c>
-      <c r="D117" s="2" t="n"/>
+      <c r="C117" s="2" t="n"/>
+      <c r="D117" s="2" t="n">
+        <v>95000</v>
+      </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Andijon Tur Servis MChJ</t>
+          <t>Qo'qon Mato MChJ</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>303911698</t>
+          <t>359614862</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>20208000572864151001</t>
+          <t>20208000130507081001</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>TOVARLAR UCHUN TO'LOV H/F №3618</t>
+          <t>Оплата по счет-фактуре №4080 за поставленный товар</t>
         </is>
       </c>
       <c r="J117" s="2" t="n">
-        <v>332207000</v>
+        <v>447811000</v>
       </c>
     </row>
     <row r="118">
@@ -4915,23 +4915,23 @@
       <c r="B118" t="n">
         <v>210</v>
       </c>
-      <c r="C118" s="2" t="n"/>
-      <c r="D118" s="2" t="n">
-        <v>920000</v>
-      </c>
+      <c r="C118" s="2" t="n">
+        <v>5098000</v>
+      </c>
+      <c r="D118" s="2" t="n"/>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Toshkent Logistik MChJ</t>
+          <t>Hududiy elektr tarmoqlari AJ</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>390251094</t>
+          <t>200933985</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>20208000862421413001</t>
+          <t>20208000977272336001</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
@@ -4941,112 +4941,117 @@
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №6284 27.08.2026, QQS bilan</t>
+          <t>Оплата за электроэнергию за август 2026 г.</t>
         </is>
       </c>
       <c r="J118" s="2" t="n">
-        <v>333127000</v>
+        <v>442713000</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="3" t="n">
-        <v>46265</v>
+        <v>46262</v>
       </c>
       <c r="B119" t="n">
         <v>211</v>
       </c>
       <c r="C119" s="2" t="n"/>
       <c r="D119" s="2" t="n">
-        <v>136000</v>
+        <v>90000</v>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Nihol Qurilish Materiallari MChJ</t>
+          <t>Navro'z Agro MChJ</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>246317566</t>
+          <t>256816338</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>20208000447981271001</t>
+          <t>20208000624445379001</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №1761 31.08.2026, QQS bilan</t>
+          <t>Оплата за товар по счет-фактуре №7275 от 28.08.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J119" s="2" t="n">
-        <v>333263000</v>
+        <v>442803000</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="3" t="n">
-        <v>46265</v>
+        <v>46262</v>
       </c>
       <c r="B120" t="n">
         <v>212</v>
       </c>
-      <c r="C120" s="2" t="n"/>
-      <c r="D120" s="2" t="n">
-        <v>111000</v>
-      </c>
+      <c r="C120" s="2" t="n">
+        <v>36092000</v>
+      </c>
+      <c r="D120" s="2" t="n"/>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Saodat Meva-Sabzavot MChJ</t>
+          <t>Farovon Sut MChJ</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>352568163</t>
+          <t>361705797</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>20208000856244453001</t>
+          <t>20208000230126901001</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №2217</t>
+          <t>Transport xizmatlari uchun to'lov, shartnoma №243/26</t>
         </is>
       </c>
       <c r="J120" s="2" t="n">
-        <v>333374000</v>
+        <v>406711000</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="3" t="n">
-        <v>46265</v>
+        <v>46262</v>
       </c>
       <c r="B121" t="n">
         <v>213</v>
       </c>
       <c r="C121" s="2" t="n">
-        <v>300000</v>
+        <v>48161000</v>
       </c>
       <c r="D121" s="2" t="n"/>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Zarafshon Kredit Bank</t>
+          <t>Oydin Mehmonxona AJ</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>339712267</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>45994000900000001001</t>
+          <t>20208000265443892001</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
@@ -5056,11 +5061,11 @@
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>Bank xizmati uchun komissiya</t>
+          <t>Оплата за товары согласно счет-фактуре №97</t>
         </is>
       </c>
       <c r="J121" s="2" t="n">
-        <v>333074000</v>
+        <v>358550000</v>
       </c>
     </row>
     <row r="122">
@@ -5070,23 +5075,23 @@
       <c r="B122" t="n">
         <v>214</v>
       </c>
-      <c r="C122" s="2" t="n">
-        <v>26158000</v>
-      </c>
-      <c r="D122" s="2" t="n"/>
+      <c r="C122" s="2" t="n"/>
+      <c r="D122" s="2" t="n">
+        <v>1438000</v>
+      </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Gulshan Poligraf MChJ</t>
+          <t>Zarafshon Poligraf MChJ</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>321061342</t>
+          <t>331756684</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>20208000490421029001</t>
+          <t>20208000798127163001</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
@@ -5096,11 +5101,11 @@
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>Materiallar uchun oldindan to'lov, shartnoma №297/26</t>
+          <t>MAHSULOT UCHUN TO'LOV, SHARTNOMA №205/26, QQS 12%</t>
         </is>
       </c>
       <c r="J122" s="2" t="n">
-        <v>306916000</v>
+        <v>359988000</v>
       </c>
     </row>
     <row r="123">
@@ -5110,143 +5115,138 @@
       <c r="B123" t="n">
         <v>215</v>
       </c>
-      <c r="C123" s="2" t="n">
-        <v>30688000</v>
-      </c>
-      <c r="D123" s="2" t="n"/>
+      <c r="C123" s="2" t="n"/>
+      <c r="D123" s="2" t="n">
+        <v>464000</v>
+      </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Andijon Tur Servis MChJ</t>
+          <t>Zarafshon Poligraf MChJ</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>303911698</t>
+          <t>331756684</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>20208000572864151001</t>
+          <t>20208000798127163001</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>Оплата за сырье по договору №27/26 от 31.08.2026, НДС 12%</t>
+          <t>Оплата по с/ф №6998 за поставленный товар</t>
         </is>
       </c>
       <c r="J123" s="2" t="n">
-        <v>276228000</v>
+        <v>360452000</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="3" t="n">
-        <v>46267</v>
+        <v>46265</v>
       </c>
       <c r="B124" t="n">
         <v>216</v>
       </c>
       <c r="C124" s="2" t="n"/>
       <c r="D124" s="2" t="n">
-        <v>26779000</v>
+        <v>200000</v>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Oltin Vodiy Mebel MChJ</t>
+          <t>Navro'z Agro MChJ</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>297197550</t>
+          <t>256816338</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>20208000006090507001</t>
+          <t>20208000624445379001</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №6676 02.09.2026, QQS bilan</t>
+          <t>Оплата за продукцию по договору №298/26, НДС 12%</t>
         </is>
       </c>
       <c r="J124" s="2" t="n">
-        <v>303007000</v>
+        <v>360652000</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="3" t="n">
-        <v>46267</v>
+        <v>46265</v>
       </c>
       <c r="B125" t="n">
         <v>217</v>
       </c>
       <c r="C125" s="2" t="n"/>
       <c r="D125" s="2" t="n">
-        <v>22963000</v>
+        <v>63000</v>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Chust Logistik MChJ</t>
+          <t>Zarafshon Poligraf MChJ</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>284027618</t>
+          <t>331756684</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>20208000325394564001</t>
+          <t>20208000798127163001</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>MAHSULOT UCHUN TO'LOV, SHARTN. №176/26, QQS 12%</t>
+          <t>Оплата по счет-фактуре №9024 за поставленный товар</t>
         </is>
       </c>
       <c r="J125" s="2" t="n">
-        <v>325970000</v>
+        <v>360715000</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="3" t="n">
-        <v>46267</v>
+        <v>46265</v>
       </c>
       <c r="B126" t="n">
         <v>218</v>
       </c>
-      <c r="C126" s="2" t="n"/>
-      <c r="D126" s="2" t="n">
-        <v>16226000</v>
-      </c>
+      <c r="C126" s="2" t="n">
+        <v>300000</v>
+      </c>
+      <c r="D126" s="2" t="n"/>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Saodat Meva-Sabzavot MChJ</t>
-        </is>
-      </c>
-      <c r="F126" t="inlineStr">
-        <is>
-          <t>352568163</t>
+          <t>Zarafshon Kredit Bank</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>20208000856244453001</t>
+          <t>45994000900000001001</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
@@ -5256,307 +5256,317 @@
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №3729</t>
+          <t>КОМИССИЯ ЗА ПЕРЕВОД</t>
         </is>
       </c>
       <c r="J126" s="2" t="n">
-        <v>342196000</v>
+        <v>360415000</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="3" t="n">
-        <v>46268</v>
+        <v>46265</v>
       </c>
       <c r="B127" t="n">
         <v>219</v>
       </c>
-      <c r="C127" s="2" t="n"/>
-      <c r="D127" s="2" t="n">
-        <v>16914000</v>
-      </c>
+      <c r="C127" s="2" t="n">
+        <v>92485000</v>
+      </c>
+      <c r="D127" s="2" t="n"/>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Nihol Qurilish Materiallari MChJ</t>
+          <t>Oydin Mehmonxona AJ</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>246317566</t>
+          <t>339712267</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>20208000447981271001</t>
+          <t>20208000265443892001</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>Shartnoma №241/26 bo'yicha oldindan to'lov</t>
+          <t>Оплата за упаковочные материалы, с/ф №9228</t>
         </is>
       </c>
       <c r="J127" s="2" t="n">
-        <v>359110000</v>
+        <v>267930000</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="3" t="n">
-        <v>46269</v>
+        <v>46266</v>
       </c>
       <c r="B128" t="n">
         <v>220</v>
       </c>
-      <c r="C128" s="2" t="n">
-        <v>19755000</v>
-      </c>
-      <c r="D128" s="2" t="n"/>
+      <c r="C128" s="2" t="n"/>
+      <c r="D128" s="2" t="n">
+        <v>6090000</v>
+      </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Oydin Plastik MChJ</t>
+          <t>Zarafshon Poligraf MChJ</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>276196667</t>
+          <t>331756684</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>20208000603938553001</t>
+          <t>20208000798127163001</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>Оплата за товары согласно счет-фактуре№6734</t>
+          <t>Оплата за продукцию по договору №162/26, НДС 12%</t>
         </is>
       </c>
       <c r="J128" s="2" t="n">
-        <v>339355000</v>
+        <v>274020000</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="3" t="n">
-        <v>46270</v>
+        <v>46266</v>
       </c>
       <c r="B129" t="n">
         <v>221</v>
       </c>
       <c r="C129" s="2" t="n">
-        <v>102400000</v>
+        <v>48106000</v>
       </c>
       <c r="D129" s="2" t="n"/>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Kreditni qaytarish hisobvarag'i (L-2025-8298)</t>
+          <t>Ziyo Qurilish Materiallari MChJ</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>291169885</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>16307000227552595417</t>
+          <t>20208000286415133001</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>Kredit shartnomasi L-2025-8298 bo'yicha navbatdagi to'lov (09.2026)</t>
+          <t>Xom ashyo uchun to'lov, shartnoma №38/26, QQS bilan</t>
         </is>
       </c>
       <c r="J129" s="2" t="n">
-        <v>236955000</v>
+        <v>225914000</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="3" t="n">
-        <v>46272</v>
+        <v>46266</v>
       </c>
       <c r="B130" t="n">
         <v>222</v>
       </c>
-      <c r="C130" s="2" t="n"/>
-      <c r="D130" s="2" t="n">
-        <v>35902000</v>
-      </c>
+      <c r="C130" s="2" t="n">
+        <v>191961000</v>
+      </c>
+      <c r="D130" s="2" t="n"/>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Nihol Qurilish Materiallari MChJ</t>
+          <t>Farg'ona Metall Servis MChJ</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>246317566</t>
+          <t>244700213</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>20208000447981271001</t>
+          <t>20208000483988736001</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartn. №228/26, QQS 12%</t>
+          <t>Оплата за сырье по договору №277/26 от 01.09.2026, НДС 12%</t>
         </is>
       </c>
       <c r="J130" s="2" t="n">
-        <v>272857000</v>
+        <v>33953000</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="3" t="n">
-        <v>46272</v>
+        <v>46267</v>
       </c>
       <c r="B131" t="n">
         <v>223</v>
       </c>
-      <c r="C131" s="2" t="n">
-        <v>8513000</v>
-      </c>
-      <c r="D131" s="2" t="n"/>
+      <c r="C131" s="2" t="n"/>
+      <c r="D131" s="2" t="n">
+        <v>43037000</v>
+      </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Ilhom Qurilish Materiallari AJ</t>
+          <t>Navro'z Agro MChJ</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>372723361</t>
+          <t>256816338</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>20208000768964202001</t>
+          <t>20208000624445379001</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>IJARA HAQI SENTYABR OYI UCHUN, SHARTNOMA №62/25</t>
+          <t>Mahsulot uchun to'lov, shartnoma №104/26, QQS 12%</t>
         </is>
       </c>
       <c r="J131" s="2" t="n">
-        <v>264344000</v>
+        <v>76990000</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="3" t="n">
-        <v>46272</v>
+        <v>46267</v>
       </c>
       <c r="B132" t="n">
         <v>224</v>
       </c>
-      <c r="C132" s="2" t="n">
-        <v>13698000</v>
-      </c>
-      <c r="D132" s="2" t="n"/>
+      <c r="C132" s="2" t="n"/>
+      <c r="D132" s="2" t="n">
+        <v>7507000</v>
+      </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Gulshan Poligraf MChJ</t>
+          <t>Navro'z Agro MChJ</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>321061342</t>
+          <t>256816338</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>20208000490421029001</t>
+          <t>20208000624445379001</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>Tovarlar uchun to'lov h/f №3743</t>
+          <t>Mahsulot uchun to'lov, shartnoma №2/26, QQS 12%</t>
         </is>
       </c>
       <c r="J132" s="2" t="n">
-        <v>250646000</v>
+        <v>84497000</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="3" t="n">
-        <v>46272</v>
+        <v>46267</v>
       </c>
       <c r="B133" t="n">
         <v>225</v>
       </c>
       <c r="C133" s="2" t="n">
-        <v>72994000</v>
+        <v>48570000</v>
       </c>
       <c r="D133" s="2" t="n"/>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Gulshan Poligraf MChJ</t>
+          <t>Ziyo Qurilish Materiallari MChJ</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>321061342</t>
+          <t>291169885</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>20208000490421029001</t>
+          <t>20208000286415133001</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>Xom ashyo uchun to'lov, shartnoma №70/26, QQS bilan</t>
+          <t>Tovarlar uchun to'lov h/f №5335</t>
         </is>
       </c>
       <c r="J133" s="2" t="n">
-        <v>177652000</v>
+        <v>35927000</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="3" t="n">
-        <v>46272</v>
+        <v>46268</v>
       </c>
       <c r="B134" t="n">
         <v>226</v>
       </c>
-      <c r="C134" s="2" t="n">
-        <v>107085000</v>
-      </c>
-      <c r="D134" s="2" t="n"/>
+      <c r="C134" s="2" t="n"/>
+      <c r="D134" s="2" t="n">
+        <v>70722000</v>
+      </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Zarafshon Kredit Bank</t>
+          <t>Zarafshon Poligraf MChJ</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>331756684</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>45994000900000001001</t>
+          <t>20208000798127163001</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
@@ -5566,37 +5576,37 @@
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>Ish haqi to'lovi avgust 2026 (plastik kartalarga)</t>
+          <t>Shartnoma №205/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
       <c r="J134" s="2" t="n">
-        <v>70567000</v>
+        <v>106649000</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="3" t="n">
-        <v>46274</v>
+        <v>46268</v>
       </c>
       <c r="B135" t="n">
         <v>227</v>
       </c>
-      <c r="C135" s="2" t="n">
-        <v>25392000</v>
-      </c>
-      <c r="D135" s="2" t="n"/>
+      <c r="C135" s="2" t="n"/>
+      <c r="D135" s="2" t="n">
+        <v>5869000</v>
+      </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Gulshan Poligraf MChJ</t>
+          <t>Zarafshon Poligraf MChJ</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>321061342</t>
+          <t>331756684</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>20208000490421029001</t>
+          <t>20208000798127163001</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
@@ -5606,277 +5616,267 @@
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>TRANSPORT XIZMATLARI UCHUN TO'LOV, SHARTNOMA №283/26</t>
+          <t>MAHSULOT UCHUN TO'LOV, SHARTNOMA №47/26, QQS 12%</t>
         </is>
       </c>
       <c r="J135" s="2" t="n">
-        <v>45175000</v>
+        <v>112518000</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="3" t="n">
-        <v>46275</v>
+        <v>46268</v>
       </c>
       <c r="B136" t="n">
         <v>228</v>
       </c>
       <c r="C136" s="2" t="n">
-        <v>45994000</v>
+        <v>31335000</v>
       </c>
       <c r="D136" s="2" t="n"/>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Yulduz Yog' Zavodi MChJ</t>
+          <t>Oqtosh Agro Servis MChJ</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>259617057</t>
+          <t>277163738</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>20208000782301269001</t>
+          <t>20208000017612936001</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>Materiallar uchun oldindan to'lov, shartnoma №105/26</t>
+          <t>Оплата за сырье по договору №135/26 от 03.09.2026, НДС 12%</t>
         </is>
       </c>
       <c r="J136" s="2" t="n">
-        <v>-819000</v>
+        <v>81183000</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="3" t="n">
-        <v>46276</v>
+        <v>46268</v>
       </c>
       <c r="B137" t="n">
         <v>229</v>
       </c>
-      <c r="C137" s="2" t="n"/>
-      <c r="D137" s="2" t="n">
-        <v>47647000</v>
-      </c>
+      <c r="C137" s="2" t="n">
+        <v>35613000</v>
+      </c>
+      <c r="D137" s="2" t="n"/>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Toshkent Logistik MChJ</t>
+          <t>Oydin Plastik XK</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>390251094</t>
+          <t>319666756</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>20208000862421413001</t>
+          <t>20208000393855383001</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №7110 от 11.09.2026, в т.ч. НДС 12%</t>
+          <t>Оплата за сырье по договору №265/26 от 03.09.2026, НДС 12%</t>
         </is>
       </c>
       <c r="J137" s="2" t="n">
-        <v>46828000</v>
+        <v>45570000</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="3" t="n">
-        <v>46279</v>
+        <v>46269</v>
       </c>
       <c r="B138" t="n">
         <v>230</v>
       </c>
       <c r="C138" s="2" t="n"/>
       <c r="D138" s="2" t="n">
-        <v>57720000</v>
+        <v>44473000</v>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Nihol Qurilish Materiallari MChJ</t>
+          <t>Zarafshon Poligraf MChJ</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>246317566</t>
+          <t>331756684</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>20208000447981271001</t>
+          <t>20208000798127163001</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>Shartnoma №245/26 bo'yicha oldindan to'lov</t>
+          <t>Оплата за товар по счет-фактуре №7265 от 04.09.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J138" s="2" t="n">
-        <v>104548000</v>
+        <v>90043000</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="3" t="n">
-        <v>46279</v>
+        <v>46269</v>
       </c>
       <c r="B139" t="n">
         <v>231</v>
       </c>
       <c r="C139" s="2" t="n"/>
       <c r="D139" s="2" t="n">
-        <v>26511000</v>
+        <v>30283000</v>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Nihol Qurilish Materiallari MChJ</t>
+          <t>Ziyo Un Mahsulotlari AJ</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>246317566</t>
+          <t>225109458</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>20208000447981271001</t>
+          <t>20208000242141305001</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, h/f №7801 14.09.2026, QQS bilan</t>
+          <t>Оплата за товар по с/ф №3251 от 04.09.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J139" s="2" t="n">
-        <v>131059000</v>
+        <v>120326000</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="3" t="n">
-        <v>46279</v>
+        <v>46269</v>
       </c>
       <c r="B140" t="n">
         <v>232</v>
       </c>
       <c r="C140" s="2" t="n">
-        <v>14603000</v>
+        <v>107085000</v>
       </c>
       <c r="D140" s="2" t="n"/>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
-        </is>
-      </c>
-      <c r="F140" t="inlineStr">
-        <is>
-          <t>201122905</t>
+          <t>Zarafshon Kredit Bank</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>45994000900000001001</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>Ijtimoiy soliq avgust 2026</t>
+          <t>Заработная плата за август 2026 г. (перечисление на пластиковые карты)</t>
         </is>
       </c>
       <c r="J140" s="2" t="n">
-        <v>116456000</v>
+        <v>13241000</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="3" t="n">
-        <v>46279</v>
+        <v>46270</v>
       </c>
       <c r="B141" t="n">
         <v>233</v>
       </c>
       <c r="C141" s="2" t="n">
-        <v>14603000</v>
+        <v>102400000</v>
       </c>
       <c r="D141" s="2" t="n"/>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
-        </is>
-      </c>
-      <c r="F141" t="inlineStr">
-        <is>
-          <t>201122905</t>
+          <t>Kreditni qaytarish hisobvarag'i (L-2025-8298)</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>16307000227552595417</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>НДФЛ за август 2026</t>
+          <t>Kredit shartnomasi L-2025-8298 bo'yicha navbatdagi to'lov (09.2026)</t>
         </is>
       </c>
       <c r="J141" s="2" t="n">
-        <v>101853000</v>
+        <v>-89159000</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="3" t="n">
-        <v>46279</v>
+        <v>46272</v>
       </c>
       <c r="B142" t="n">
         <v>234</v>
       </c>
-      <c r="C142" s="2" t="n">
-        <v>18103000</v>
-      </c>
-      <c r="D142" s="2" t="n"/>
+      <c r="C142" s="2" t="n"/>
+      <c r="D142" s="2" t="n">
+        <v>93759000</v>
+      </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Gulshan Poligraf MChJ</t>
+          <t>Zarafshon Poligraf MChJ</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>321061342</t>
+          <t>331756684</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>20208000490421029001</t>
+          <t>20208000798127163001</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
@@ -5886,37 +5886,37 @@
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>Оплата за транспортные услуги по договору №104/26</t>
+          <t>Предоплата за товар по договору №278/26 от 07.09.2026</t>
         </is>
       </c>
       <c r="J142" s="2" t="n">
-        <v>83750000</v>
+        <v>4600000</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="3" t="n">
-        <v>46279</v>
+        <v>46272</v>
       </c>
       <c r="B143" t="n">
         <v>235</v>
       </c>
-      <c r="C143" s="2" t="n">
-        <v>32860000</v>
-      </c>
-      <c r="D143" s="2" t="n"/>
+      <c r="C143" s="2" t="n"/>
+      <c r="D143" s="2" t="n">
+        <v>27700000</v>
+      </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Gulshan Poligraf MChJ</t>
+          <t>Zarafshon Poligraf MChJ</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>321061342</t>
+          <t>331756684</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>20208000490421029001</t>
+          <t>20208000798127163001</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
@@ -5926,437 +5926,437 @@
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>Xom ashyo uchun to'lov, shartn. №96/26, QQS bilan</t>
+          <t>Оплата за продукцию по договору №262/26, НДС 12%</t>
         </is>
       </c>
       <c r="J143" s="2" t="n">
-        <v>50890000</v>
+        <v>32300000</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="3" t="n">
-        <v>46279</v>
+        <v>46272</v>
       </c>
       <c r="B144" t="n">
         <v>236</v>
       </c>
-      <c r="C144" s="2" t="n">
-        <v>64672000</v>
-      </c>
-      <c r="D144" s="2" t="n"/>
+      <c r="C144" s="2" t="n"/>
+      <c r="D144" s="2" t="n">
+        <v>14492000</v>
+      </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Andijon Tur Servis MChJ</t>
+          <t>Zarafshon Poligraf MChJ</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>303911698</t>
+          <t>331756684</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>20208000572864151001</t>
+          <t>20208000798127163001</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>Transport xizmatlari uchun to'lov, shartnoma №215/26</t>
+          <t>SHARTNOMA №247/26 BO'YICHA OLDINDAN TO'LOV</t>
         </is>
       </c>
       <c r="J144" s="2" t="n">
-        <v>-13782000</v>
+        <v>46792000</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="3" t="n">
-        <v>46279</v>
+        <v>46272</v>
       </c>
       <c r="B145" t="n">
         <v>237</v>
       </c>
-      <c r="C145" s="2" t="n">
-        <v>262282000</v>
-      </c>
-      <c r="D145" s="2" t="n"/>
+      <c r="C145" s="2" t="n"/>
+      <c r="D145" s="2" t="n">
+        <v>10544000</v>
+      </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Gulshan Poligraf MChJ</t>
+          <t>Navro'z Agro MChJ</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>321061342</t>
+          <t>256816338</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>20208000490421029001</t>
+          <t>20208000624445379001</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>Xom ashyo uchun to'lov, shartn. №136/26, QQS bilan</t>
+          <t>Оплата за продукцию по договору №3/26, НДС 12%</t>
         </is>
       </c>
       <c r="J145" s="2" t="n">
-        <v>-276064000</v>
+        <v>57336000</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="3" t="n">
-        <v>46280</v>
+        <v>46272</v>
       </c>
       <c r="B146" t="n">
         <v>238</v>
       </c>
       <c r="C146" s="2" t="n"/>
       <c r="D146" s="2" t="n">
-        <v>28947000</v>
+        <v>10516000</v>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Nihol Qurilish Materiallari MChJ</t>
+          <t>Zarafshon Poligraf MChJ</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>246317566</t>
+          <t>331756684</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>20208000447981271001</t>
+          <t>20208000798127163001</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>Shartnoma №68/26 bo'yicha oldindan to'lov</t>
+          <t>Оплата за товар по счет-фактуре №1729 от 07.09.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J146" s="2" t="n">
-        <v>-247117000</v>
+        <v>67852000</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="3" t="n">
-        <v>46281</v>
+        <v>46272</v>
       </c>
       <c r="B147" t="n">
         <v>239</v>
       </c>
       <c r="C147" s="2" t="n"/>
       <c r="D147" s="2" t="n">
-        <v>30185000</v>
+        <v>10294000</v>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Nihol Qurilish Materiallari MChJ</t>
+          <t>Qo'qon Mato MChJ</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>246317566</t>
+          <t>359614862</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>20208000447981271001</t>
+          <t>20208000130507081001</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>MAHSULOT UCHUN TO'LOV, SHARTNOMA №292/26, QQS 12%</t>
+          <t>Предоплата за товар по дог. №283/26 от 07.09.2026</t>
         </is>
       </c>
       <c r="J147" s="2" t="n">
-        <v>-216932000</v>
+        <v>78146000</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="3" t="n">
-        <v>46281</v>
+        <v>46272</v>
       </c>
       <c r="B148" t="n">
         <v>240</v>
       </c>
-      <c r="C148" s="2" t="n"/>
-      <c r="D148" s="2" t="n">
-        <v>18926000</v>
-      </c>
+      <c r="C148" s="2" t="n">
+        <v>117900000</v>
+      </c>
+      <c r="D148" s="2" t="n"/>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Nihol Qurilish Materiallari MChJ</t>
+          <t>Farg'ona Metall Servis MChJ</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>246317566</t>
+          <t>244700213</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>20208000447981271001</t>
+          <t>20208000483988736001</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, h/f №5417 16.09.2026, QQS bilan</t>
+          <t>Оплата за товары согласно с/ф №4993</t>
         </is>
       </c>
       <c r="J148" s="2" t="n">
-        <v>-198006000</v>
+        <v>-39754000</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="3" t="n">
-        <v>46281</v>
+        <v>46272</v>
       </c>
       <c r="B149" t="n">
         <v>241</v>
       </c>
-      <c r="C149" s="2" t="n"/>
-      <c r="D149" s="2" t="n">
-        <v>15269000</v>
-      </c>
+      <c r="C149" s="2" t="n">
+        <v>216602000</v>
+      </c>
+      <c r="D149" s="2" t="n"/>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Saodat Meva-Sabzavot MChJ</t>
+          <t>Farg'ona Metall Servis MChJ</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>352568163</t>
+          <t>244700213</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>20208000856244453001</t>
+          <t>20208000483988736001</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t>MAHSULOT UCHUN TO'LOV, SHARTNOMA №227/26, QQS 12%</t>
+          <t>Оплата за транспортные услуги по договору №128/26</t>
         </is>
       </c>
       <c r="J149" s="2" t="n">
-        <v>-182737000</v>
+        <v>-256356000</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="3" t="n">
-        <v>46282</v>
+        <v>46273</v>
       </c>
       <c r="B150" t="n">
         <v>242</v>
       </c>
       <c r="C150" s="2" t="n"/>
       <c r="D150" s="2" t="n">
-        <v>73509000</v>
+        <v>318969000</v>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Nihol Qurilish Materiallari MChJ</t>
+          <t>Zarafshon Poligraf MChJ</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>246317566</t>
+          <t>331756684</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>20208000447981271001</t>
+          <t>20208000798127163001</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №6198</t>
+          <t>Оплата за товар по с/ф №5168 от 08.09.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J150" s="2" t="n">
-        <v>-109228000</v>
+        <v>62613000</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="3" t="n">
-        <v>46282</v>
+        <v>46273</v>
       </c>
       <c r="B151" t="n">
         <v>243</v>
       </c>
       <c r="C151" s="2" t="n"/>
       <c r="D151" s="2" t="n">
-        <v>33741000</v>
+        <v>5326000</v>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Nihol Qurilish Materiallari MChJ</t>
+          <t>Zarafshon Poligraf MChJ</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>246317566</t>
+          <t>331756684</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>20208000447981271001</t>
+          <t>20208000798127163001</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №87/26 от 17.09.2026</t>
+          <t>MAHSULOT UCHUN TO'LOV, SHARTN. №82/26, QQS 12%</t>
         </is>
       </c>
       <c r="J151" s="2" t="n">
-        <v>-75487000</v>
+        <v>67939000</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="3" t="n">
-        <v>46282</v>
+        <v>46273</v>
       </c>
       <c r="B152" t="n">
         <v>244</v>
       </c>
       <c r="C152" s="2" t="n">
-        <v>10785000</v>
+        <v>23707000</v>
       </c>
       <c r="D152" s="2" t="n"/>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Andijon Tur Servis MChJ</t>
+          <t>Oydin Plastik XK</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>303911698</t>
+          <t>319666756</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>20208000572864151001</t>
+          <t>20208000393855383001</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>Transport xizmatlari uchun to'lov, shartnoma №172/26</t>
+          <t>Оплата за сырье по договору №44/26 от 08.09.2026, НДС 12%</t>
         </is>
       </c>
       <c r="J152" s="2" t="n">
-        <v>-86272000</v>
+        <v>44232000</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="3" t="n">
-        <v>46283</v>
+        <v>46274</v>
       </c>
       <c r="B153" t="n">
         <v>245</v>
       </c>
       <c r="C153" s="2" t="n"/>
       <c r="D153" s="2" t="n">
-        <v>12860000</v>
+        <v>59909000</v>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Nihol Qurilish Materiallari MChJ</t>
+          <t>Sarbon Mebel XK</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>246317566</t>
+          <t>202761813</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>20208000447981271001</t>
+          <t>20208000539456465001</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №35/26, QQS 12%</t>
+          <t>Оплата за товар по счет-фактуре №5134 от 09.09.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J153" s="2" t="n">
-        <v>-73412000</v>
+        <v>104141000</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="3" t="n">
-        <v>46286</v>
+        <v>46274</v>
       </c>
       <c r="B154" t="n">
         <v>246</v>
       </c>
       <c r="C154" s="2" t="n"/>
       <c r="D154" s="2" t="n">
-        <v>37608000</v>
+        <v>12393000</v>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Saodat Meva-Sabzavot MChJ</t>
+          <t>Zarafshon Poligraf MChJ</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>352568163</t>
+          <t>331756684</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>20208000856244453001</t>
+          <t>20208000798127163001</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
@@ -6366,197 +6366,197 @@
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t>Оплата по с/ф №1631 за поставленный товар</t>
+          <t>Предоплата за товар по договору №216/26 от 09.09.2026</t>
         </is>
       </c>
       <c r="J154" s="2" t="n">
-        <v>-35804000</v>
+        <v>116534000</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="3" t="n">
-        <v>46286</v>
+        <v>46274</v>
       </c>
       <c r="B155" t="n">
         <v>247</v>
       </c>
-      <c r="C155" s="2" t="n"/>
-      <c r="D155" s="2" t="n">
-        <v>12655000</v>
-      </c>
+      <c r="C155" s="2" t="n">
+        <v>8513000</v>
+      </c>
+      <c r="D155" s="2" t="n"/>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Saodat Meva-Sabzavot MChJ</t>
+          <t>Shodlik Qurilish MChJ</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>352568163</t>
+          <t>354336802</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>20208000856244453001</t>
+          <t>20208000212400074001</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t>TOVAR UCHUN TO'LOV, H/F №937 21.09.2026, QQS BILAN</t>
+          <t>АРЕНДНАЯ ПЛАТА ЗА СЕНТЯБРЬ 2026 Г. ПО ДОГОВОРУ №93/24</t>
         </is>
       </c>
       <c r="J155" s="2" t="n">
-        <v>-23149000</v>
+        <v>108021000</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="3" t="n">
-        <v>46286</v>
+        <v>46276</v>
       </c>
       <c r="B156" t="n">
         <v>248</v>
       </c>
-      <c r="C156" s="2" t="n">
-        <v>13522000</v>
-      </c>
-      <c r="D156" s="2" t="n"/>
+      <c r="C156" s="2" t="n"/>
+      <c r="D156" s="2" t="n">
+        <v>8348000</v>
+      </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Gulshan Poligraf MChJ</t>
+          <t>Ziyo Un Mahsulotlari AJ</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>321061342</t>
+          <t>225109458</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>20208000490421029001</t>
+          <t>20208000242141305001</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t>Materiallar uchun oldindan to'lov, shartn. №150/26</t>
+          <t>Оплата по с/ф №431 за поставленный товар</t>
         </is>
       </c>
       <c r="J156" s="2" t="n">
-        <v>-36671000</v>
+        <v>116369000</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="3" t="n">
-        <v>46286</v>
+        <v>46279</v>
       </c>
       <c r="B157" t="n">
         <v>249</v>
       </c>
-      <c r="C157" s="2" t="n">
-        <v>14188000</v>
-      </c>
-      <c r="D157" s="2" t="n"/>
+      <c r="C157" s="2" t="n"/>
+      <c r="D157" s="2" t="n">
+        <v>20576000</v>
+      </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Zarafshon Poligraf MChJ</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>331756684</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000798127163001</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t>QQS avgust 2026 uchun</t>
+          <t>Предоплата за товар по договору №246/26 от 14.09.2026</t>
         </is>
       </c>
       <c r="J157" s="2" t="n">
-        <v>-50859000</v>
+        <v>136945000</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="3" t="n">
-        <v>46286</v>
+        <v>46279</v>
       </c>
       <c r="B158" t="n">
         <v>250</v>
       </c>
-      <c r="C158" s="2" t="n">
-        <v>23674000</v>
-      </c>
-      <c r="D158" s="2" t="n"/>
+      <c r="C158" s="2" t="n"/>
+      <c r="D158" s="2" t="n">
+        <v>7405000</v>
+      </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Andijon Tur Servis MChJ</t>
+          <t>Sarbon Mebel XK</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>303911698</t>
+          <t>202761813</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>20208000572864151001</t>
+          <t>20208000539456465001</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t>Transport xizmatlari uchun to'lov, shartnoma №93/26</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №7483</t>
         </is>
       </c>
       <c r="J158" s="2" t="n">
-        <v>-74533000</v>
+        <v>144350000</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="3" t="n">
-        <v>46286</v>
+        <v>46280</v>
       </c>
       <c r="B159" t="n">
         <v>251</v>
       </c>
-      <c r="C159" s="2" t="n">
-        <v>45471000</v>
-      </c>
-      <c r="D159" s="2" t="n"/>
+      <c r="C159" s="2" t="n"/>
+      <c r="D159" s="2" t="n">
+        <v>15486000</v>
+      </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Gulshan Poligraf MChJ</t>
+          <t>Zarafshon Poligraf MChJ</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>321061342</t>
+          <t>331756684</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>20208000490421029001</t>
+          <t>20208000798127163001</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
@@ -6566,277 +6566,277 @@
       </c>
       <c r="I159" t="inlineStr">
         <is>
-          <t>Xom ashyo uchun to'lov, shartnoma №09/26, QQS bilan</t>
+          <t>Оплата по с/ф №788 за поставленный товар</t>
         </is>
       </c>
       <c r="J159" s="2" t="n">
-        <v>-120004000</v>
+        <v>159836000</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="3" t="n">
-        <v>46286</v>
+        <v>46280</v>
       </c>
       <c r="B160" t="n">
         <v>252</v>
       </c>
-      <c r="C160" s="2" t="n">
-        <v>192115000</v>
-      </c>
-      <c r="D160" s="2" t="n"/>
+      <c r="C160" s="2" t="n"/>
+      <c r="D160" s="2" t="n">
+        <v>5869000</v>
+      </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Gulshan Poligraf MChJ</t>
+          <t>Navro'z Agro MChJ</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>321061342</t>
+          <t>256816338</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>20208000490421029001</t>
+          <t>20208000624445379001</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t>ОПЛАТА ЗА ТРАНСПОРТНЫЕ УСЛУГИ ПО ДОГ. №180/26</t>
+          <t>Оплата за продукцию по договору №266/26, НДС 12%</t>
         </is>
       </c>
       <c r="J160" s="2" t="n">
-        <v>-312119000</v>
+        <v>165705000</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="3" t="n">
-        <v>46287</v>
+        <v>46281</v>
       </c>
       <c r="B161" t="n">
         <v>253</v>
       </c>
-      <c r="C161" s="2" t="n"/>
-      <c r="D161" s="2" t="n">
-        <v>34377000</v>
-      </c>
+      <c r="C161" s="2" t="n">
+        <v>14603000</v>
+      </c>
+      <c r="D161" s="2" t="n"/>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Chust Logistik MChJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>284027618</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>20208000325394564001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I161" t="inlineStr">
         <is>
-          <t>ОПЛАТА ЗА ТОВАР ПО СЧЕТ-ФАКТУРЕ №4966 ОТ 22.09.2026, В Т.Ч. НДС 12%</t>
+          <t>Социальный налог за август 2026 г.</t>
         </is>
       </c>
       <c r="J161" s="2" t="n">
-        <v>-277742000</v>
+        <v>151102000</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="3" t="n">
-        <v>46287</v>
+        <v>46281</v>
       </c>
       <c r="B162" t="n">
         <v>254</v>
       </c>
-      <c r="C162" s="2" t="n"/>
-      <c r="D162" s="2" t="n">
-        <v>31988000</v>
-      </c>
+      <c r="C162" s="2" t="n">
+        <v>14603000</v>
+      </c>
+      <c r="D162" s="2" t="n"/>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Nihol Qurilish Materiallari MChJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>246317566</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>20208000447981271001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartn. №68/26, QQS 12%</t>
+          <t>Налог на доходы физических лиц за август 2026 г.</t>
         </is>
       </c>
       <c r="J162" s="2" t="n">
-        <v>-245754000</v>
+        <v>136499000</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="3" t="n">
-        <v>46288</v>
+        <v>46281</v>
       </c>
       <c r="B163" t="n">
         <v>255</v>
       </c>
-      <c r="C163" s="2" t="n"/>
-      <c r="D163" s="2" t="n">
-        <v>32331000</v>
-      </c>
+      <c r="C163" s="2" t="n">
+        <v>17898000</v>
+      </c>
+      <c r="D163" s="2" t="n"/>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Toshkent Logistik MChJ</t>
+          <t>Oqtosh Agro Servis MChJ</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>390251094</t>
+          <t>277163738</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>20208000862421413001</t>
+          <t>20208000017612936001</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I163" t="inlineStr">
         <is>
-          <t>Shartnoma №70/26 bo'yicha oldindan to'lov</t>
+          <t>Оплата за упаковочные материалы, с/ф №418</t>
         </is>
       </c>
       <c r="J163" s="2" t="n">
-        <v>-213423000</v>
+        <v>118601000</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="3" t="n">
-        <v>46288</v>
+        <v>46282</v>
       </c>
       <c r="B164" t="n">
         <v>256</v>
       </c>
       <c r="C164" s="2" t="n"/>
       <c r="D164" s="2" t="n">
-        <v>12859000</v>
+        <v>23274000</v>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Nihol Qurilish Materiallari MChJ</t>
+          <t>Zarafshon Poligraf MChJ</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>246317566</t>
+          <t>331756684</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>20208000447981271001</t>
+          <t>20208000798127163001</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I164" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №6355 23.09.2026, QQS bilan</t>
+          <t>Shartnoma №270/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
       <c r="J164" s="2" t="n">
-        <v>-200564000</v>
+        <v>141875000</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="3" t="n">
-        <v>46289</v>
+        <v>46283</v>
       </c>
       <c r="B165" t="n">
         <v>257</v>
       </c>
       <c r="C165" s="2" t="n"/>
       <c r="D165" s="2" t="n">
-        <v>21559000</v>
+        <v>48219000</v>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Saodat Meva-Sabzavot MChJ</t>
+          <t>Qo'qon Mato MChJ</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>352568163</t>
+          <t>359614862</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>20208000856244453001</t>
+          <t>20208000130507081001</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I165" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по дог. №2/26, НДС 12%</t>
+          <t>Оплата за продукцию по договору №173/26, НДС 12%</t>
         </is>
       </c>
       <c r="J165" s="2" t="n">
-        <v>-179005000</v>
+        <v>190094000</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="3" t="n">
-        <v>46289</v>
+        <v>46286</v>
       </c>
       <c r="B166" t="n">
         <v>258</v>
       </c>
       <c r="C166" s="2" t="n"/>
       <c r="D166" s="2" t="n">
-        <v>16448000</v>
+        <v>43782000</v>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Bahor Meva Eksport MChJ</t>
+          <t>Zarafshon Poligraf MChJ</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>207825049</t>
+          <t>331756684</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>20208000822969351001</t>
+          <t>20208000798127163001</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
@@ -6846,157 +6846,157 @@
       </c>
       <c r="I166" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №3572</t>
+          <t>Оплата за продукцию по договору №133/26, НДС 12%</t>
         </is>
       </c>
       <c r="J166" s="2" t="n">
-        <v>-162557000</v>
+        <v>233876000</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="3" t="n">
-        <v>46289</v>
+        <v>46286</v>
       </c>
       <c r="B167" t="n">
         <v>259</v>
       </c>
-      <c r="C167" s="2" t="n">
-        <v>66613000</v>
-      </c>
-      <c r="D167" s="2" t="n"/>
+      <c r="C167" s="2" t="n"/>
+      <c r="D167" s="2" t="n">
+        <v>16339000</v>
+      </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Bunyodkor Yog'och XK</t>
+          <t>Navro'z Agro MChJ</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>200938755</t>
+          <t>256816338</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>20208000615898491001</t>
+          <t>20208000624445379001</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t>Оплата за упаковочные материалы, с/ф №2637</t>
+          <t>Shartnoma №46/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
       <c r="J167" s="2" t="n">
-        <v>-229170000</v>
+        <v>250215000</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="3" t="n">
-        <v>46290</v>
+        <v>46286</v>
       </c>
       <c r="B168" t="n">
         <v>260</v>
       </c>
       <c r="C168" s="2" t="n"/>
       <c r="D168" s="2" t="n">
-        <v>163536000</v>
+        <v>14181000</v>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Nihol Qurilish Materiallari MChJ</t>
+          <t>Qo'qon Mato MChJ</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>246317566</t>
+          <t>359614862</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>20208000447981271001</t>
+          <t>20208000130507081001</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I168" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №9612</t>
+          <t>Оплата по счет-фактуре №1618 за поставленный товар</t>
         </is>
       </c>
       <c r="J168" s="2" t="n">
-        <v>-65634000</v>
+        <v>264396000</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="3" t="n">
-        <v>46290</v>
+        <v>46286</v>
       </c>
       <c r="B169" t="n">
         <v>261</v>
       </c>
       <c r="C169" s="2" t="n"/>
       <c r="D169" s="2" t="n">
-        <v>131264000</v>
+        <v>6810000</v>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Nihol Qurilish Materiallari MChJ</t>
+          <t>Ziyo Un Mahsulotlari AJ</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>246317566</t>
+          <t>225109458</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>20208000447981271001</t>
+          <t>20208000242141305001</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I169" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №4911</t>
+          <t>Оплата по сет-фактуре №1434 за поставленный товар</t>
         </is>
       </c>
       <c r="J169" s="2" t="n">
-        <v>65630000</v>
+        <v>271206000</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="3" t="n">
-        <v>46290</v>
+        <v>46286</v>
       </c>
       <c r="B170" t="n">
         <v>262</v>
       </c>
       <c r="C170" s="2" t="n"/>
       <c r="D170" s="2" t="n">
-        <v>20321000</v>
+        <v>5635000</v>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Saodat Meva-Sabzavot MChJ</t>
+          <t>Zarafshon Poligraf MChJ</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>352568163</t>
+          <t>331756684</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>20208000856244453001</t>
+          <t>20208000798127163001</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
@@ -7006,391 +7006,711 @@
       </c>
       <c r="I170" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №5707 25.09.2026, QQS bilan</t>
+          <t>Оплата за продукцию по дог. №12/26, НДС 12%</t>
         </is>
       </c>
       <c r="J170" s="2" t="n">
-        <v>85951000</v>
+        <v>276841000</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" s="3" t="n">
-        <v>46293</v>
+        <v>46286</v>
       </c>
       <c r="B171" t="n">
         <v>263</v>
       </c>
-      <c r="C171" s="2" t="n"/>
-      <c r="D171" s="2" t="n">
-        <v>33930000</v>
-      </c>
+      <c r="C171" s="2" t="n">
+        <v>82359000</v>
+      </c>
+      <c r="D171" s="2" t="n"/>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Nihol Qurilish Materiallari MChJ</t>
+          <t>Farg'ona Metall Servis MChJ</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>246317566</t>
+          <t>244700213</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>20208000447981271001</t>
+          <t>20208000483988736001</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I171" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по дог. №95/26, НДС 12%</t>
+          <t>Оплата за транспортные услуги по дог. №46/26</t>
         </is>
       </c>
       <c r="J171" s="2" t="n">
-        <v>119881000</v>
+        <v>194482000</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="3" t="n">
-        <v>46293</v>
+        <v>46287</v>
       </c>
       <c r="B172" t="n">
         <v>264</v>
       </c>
-      <c r="C172" s="2" t="n"/>
-      <c r="D172" s="2" t="n">
-        <v>21848000</v>
-      </c>
+      <c r="C172" s="2" t="n">
+        <v>14080000</v>
+      </c>
+      <c r="D172" s="2" t="n"/>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Saodat Meva-Sabzavot MChJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>352568163</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>20208000856244453001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I172" t="inlineStr">
         <is>
-          <t>MAHSULOT UCHUN TO'LOV, SHARTNOMA №201/26, QQS 12%</t>
+          <t>Уплата налога на добавленную стоимость за август</t>
         </is>
       </c>
       <c r="J172" s="2" t="n">
-        <v>141729000</v>
+        <v>180402000</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" s="3" t="n">
-        <v>46293</v>
+        <v>46287</v>
       </c>
       <c r="B173" t="n">
         <v>265</v>
       </c>
-      <c r="C173" s="2" t="n"/>
-      <c r="D173" s="2" t="n">
-        <v>16488000</v>
-      </c>
+      <c r="C173" s="2" t="n">
+        <v>22573000</v>
+      </c>
+      <c r="D173" s="2" t="n"/>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Saodat Meva-Sabzavot MChJ</t>
+          <t>Farg'ona Metall Servis MChJ</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>352568163</t>
+          <t>244700213</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>20208000856244453001</t>
+          <t>20208000483988736001</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I173" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №6466 28.09.2026, QQS bilan</t>
+          <t>ОПЛАТА ЗА ТОВАРЫ СОГЛАСНО СЧЕТ-ФАКТУРЕ №9436</t>
         </is>
       </c>
       <c r="J173" s="2" t="n">
-        <v>158217000</v>
+        <v>157829000</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" s="3" t="n">
-        <v>46293</v>
+        <v>46288</v>
       </c>
       <c r="B174" t="n">
         <v>266</v>
       </c>
       <c r="C174" s="2" t="n"/>
       <c r="D174" s="2" t="n">
-        <v>15961000</v>
+        <v>25862000</v>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Xiva Sut AJ</t>
+          <t>Zarafshon Poligraf MChJ</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>259596148</t>
+          <t>331756684</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>20208000211305070001</t>
+          <t>20208000798127163001</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I174" t="inlineStr">
         <is>
-          <t>MAHSULOT UCHUN TO'LOV, SHARTNOMA №201/26, QQS 12%</t>
+          <t>Оплата за товар по с/ф №1313 от 23.09.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J174" s="2" t="n">
-        <v>174178000</v>
+        <v>183691000</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" s="3" t="n">
-        <v>46293</v>
+        <v>46289</v>
       </c>
       <c r="B175" t="n">
         <v>267</v>
       </c>
       <c r="C175" s="2" t="n"/>
       <c r="D175" s="2" t="n">
-        <v>12906000</v>
+        <v>11545000</v>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Nihol Qurilish Materiallari MChJ</t>
+          <t>Zarafshon Poligraf MChJ</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>246317566</t>
+          <t>331756684</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>20208000447981271001</t>
+          <t>20208000798127163001</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I175" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №5911 28.09.2026, QQS bilan</t>
+          <t>Оплата за товар по счет-фактуре №5945 от 24.09.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J175" s="2" t="n">
-        <v>187084000</v>
+        <v>195236000</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" s="3" t="n">
-        <v>46293</v>
+        <v>46290</v>
       </c>
       <c r="B176" t="n">
         <v>268</v>
       </c>
       <c r="C176" s="2" t="n">
-        <v>5321000</v>
+        <v>37513000</v>
       </c>
       <c r="D176" s="2" t="n"/>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Hududiy elektr tarmoqlari AJ</t>
+          <t>Oydin Mehmonxona AJ</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>200933985</t>
+          <t>339712267</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>20208000322645921001</t>
+          <t>20208000265443892001</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I176" t="inlineStr">
         <is>
-          <t>Elektr energiyasi uchun to'lov</t>
+          <t>Оплата за транспортные услуги по договору №277/26</t>
         </is>
       </c>
       <c r="J176" s="2" t="n">
-        <v>181763000</v>
+        <v>157723000</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" s="3" t="n">
-        <v>46294</v>
+        <v>46293</v>
       </c>
       <c r="B177" t="n">
         <v>269</v>
       </c>
       <c r="C177" s="2" t="n"/>
       <c r="D177" s="2" t="n">
-        <v>90725000</v>
+        <v>32378000</v>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Nihol Qurilish Materiallari MChJ</t>
+          <t>Zarafshon Poligraf MChJ</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>246317566</t>
+          <t>331756684</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>20208000447981271001</t>
+          <t>20208000798127163001</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I177" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №9661 29.09.2026, QQS bilan</t>
+          <t>Оплата за товар по счет-фактуре №6720 от 28.09.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J177" s="2" t="n">
-        <v>272488000</v>
+        <v>190101000</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" s="3" t="n">
-        <v>46294</v>
+        <v>46293</v>
       </c>
       <c r="B178" t="n">
         <v>270</v>
       </c>
       <c r="C178" s="2" t="n"/>
       <c r="D178" s="2" t="n">
-        <v>11412000</v>
+        <v>25256000</v>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Nihol Qurilish Materiallari MChJ</t>
+          <t>Zarafshon Poligraf MChJ</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>246317566</t>
+          <t>331756684</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>20208000447981271001</t>
+          <t>20208000798127163001</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I178" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №269/26 от 29.09.2026</t>
+          <t>Mahsulot uchun to'lov, shartnoma №76/26, QQS 12%</t>
         </is>
       </c>
       <c r="J178" s="2" t="n">
-        <v>283900000</v>
+        <v>215357000</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" s="3" t="n">
-        <v>46295</v>
+        <v>46293</v>
       </c>
       <c r="B179" t="n">
         <v>271</v>
       </c>
-      <c r="C179" s="2" t="n">
+      <c r="C179" s="2" t="n"/>
+      <c r="D179" s="2" t="n">
+        <v>21965000</v>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>Qo'qon Mato MChJ</t>
+        </is>
+      </c>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>359614862</t>
+        </is>
+      </c>
+      <c r="G179" t="inlineStr">
+        <is>
+          <t>20208000130507081001</t>
+        </is>
+      </c>
+      <c r="H179" t="inlineStr">
+        <is>
+          <t>01121</t>
+        </is>
+      </c>
+      <c r="I179" t="inlineStr">
+        <is>
+          <t>Оплата за продукцию по дог. №45/26, НДС 12%</t>
+        </is>
+      </c>
+      <c r="J179" s="2" t="n">
+        <v>237322000</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="3" t="n">
+        <v>46293</v>
+      </c>
+      <c r="B180" t="n">
+        <v>272</v>
+      </c>
+      <c r="C180" s="2" t="n"/>
+      <c r="D180" s="2" t="n">
+        <v>20661000</v>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>Zarafshon Poligraf MChJ</t>
+        </is>
+      </c>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>331756684</t>
+        </is>
+      </c>
+      <c r="G180" t="inlineStr">
+        <is>
+          <t>20208000798127163001</t>
+        </is>
+      </c>
+      <c r="H180" t="inlineStr">
+        <is>
+          <t>00987</t>
+        </is>
+      </c>
+      <c r="I180" t="inlineStr">
+        <is>
+          <t>Tovar uchun to'lov, hisob-faktura №867 28.09.2026, QQS bilan</t>
+        </is>
+      </c>
+      <c r="J180" s="2" t="n">
+        <v>257983000</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="3" t="n">
+        <v>46293</v>
+      </c>
+      <c r="B181" t="n">
+        <v>273</v>
+      </c>
+      <c r="C181" s="2" t="n"/>
+      <c r="D181" s="2" t="n">
+        <v>12099000</v>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>Zarafshon Poligraf MChJ</t>
+        </is>
+      </c>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>331756684</t>
+        </is>
+      </c>
+      <c r="G181" t="inlineStr">
+        <is>
+          <t>20208000798127163001</t>
+        </is>
+      </c>
+      <c r="H181" t="inlineStr">
+        <is>
+          <t>00987</t>
+        </is>
+      </c>
+      <c r="I181" t="inlineStr">
+        <is>
+          <t>Yetkazilgan tovar uchun to'lov h/f №1855</t>
+        </is>
+      </c>
+      <c r="J181" s="2" t="n">
+        <v>270082000</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="3" t="n">
+        <v>46293</v>
+      </c>
+      <c r="B182" t="n">
+        <v>274</v>
+      </c>
+      <c r="C182" s="2" t="n"/>
+      <c r="D182" s="2" t="n">
+        <v>10199000</v>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>Qo'qon Mato MChJ</t>
+        </is>
+      </c>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>359614862</t>
+        </is>
+      </c>
+      <c r="G182" t="inlineStr">
+        <is>
+          <t>20208000130507081001</t>
+        </is>
+      </c>
+      <c r="H182" t="inlineStr">
+        <is>
+          <t>01121</t>
+        </is>
+      </c>
+      <c r="I182" t="inlineStr">
+        <is>
+          <t>ПРЕДОПЛАТА ЗА ТОВАР ПО ДОГОВОРУ №64/26 ОТ 28.09.2026</t>
+        </is>
+      </c>
+      <c r="J182" s="2" t="n">
+        <v>280281000</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="3" t="n">
+        <v>46293</v>
+      </c>
+      <c r="B183" t="n">
+        <v>275</v>
+      </c>
+      <c r="C183" s="2" t="n">
+        <v>5321000</v>
+      </c>
+      <c r="D183" s="2" t="n"/>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>Hududiy elektr tarmoqlari AJ</t>
+        </is>
+      </c>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>200933985</t>
+        </is>
+      </c>
+      <c r="G183" t="inlineStr">
+        <is>
+          <t>20208000977272336001</t>
+        </is>
+      </c>
+      <c r="H183" t="inlineStr">
+        <is>
+          <t>01204</t>
+        </is>
+      </c>
+      <c r="I183" t="inlineStr">
+        <is>
+          <t>Оплата за электроэнергию согласно счету</t>
+        </is>
+      </c>
+      <c r="J183" s="2" t="n">
+        <v>274960000</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="3" t="n">
+        <v>46293</v>
+      </c>
+      <c r="B184" t="n">
+        <v>276</v>
+      </c>
+      <c r="C184" s="2" t="n">
+        <v>16581000</v>
+      </c>
+      <c r="D184" s="2" t="n"/>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>Farg'ona Metall Servis MChJ</t>
+        </is>
+      </c>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t>244700213</t>
+        </is>
+      </c>
+      <c r="G184" t="inlineStr">
+        <is>
+          <t>20208000483988736001</t>
+        </is>
+      </c>
+      <c r="H184" t="inlineStr">
+        <is>
+          <t>01153</t>
+        </is>
+      </c>
+      <c r="I184" t="inlineStr">
+        <is>
+          <t>Оплата за товары согласно счет-фактуре №4337</t>
+        </is>
+      </c>
+      <c r="J184" s="2" t="n">
+        <v>258379000</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="B185" t="n">
+        <v>277</v>
+      </c>
+      <c r="C185" s="2" t="n"/>
+      <c r="D185" s="2" t="n">
+        <v>7284000</v>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>Zarafshon Poligraf MChJ</t>
+        </is>
+      </c>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t>331756684</t>
+        </is>
+      </c>
+      <c r="G185" t="inlineStr">
+        <is>
+          <t>20208000798127163001</t>
+        </is>
+      </c>
+      <c r="H185" t="inlineStr">
+        <is>
+          <t>00987</t>
+        </is>
+      </c>
+      <c r="I185" t="inlineStr">
+        <is>
+          <t>Оплата за товар по счет-фактуре №9620 от 29.09.2026, в т.ч. НДС 12%</t>
+        </is>
+      </c>
+      <c r="J185" s="2" t="n">
+        <v>265663000</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="3" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B186" t="n">
+        <v>278</v>
+      </c>
+      <c r="C186" s="2" t="n"/>
+      <c r="D186" s="2" t="n">
+        <v>18237000</v>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>Nukus Sut AJ</t>
+        </is>
+      </c>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>206223363</t>
+        </is>
+      </c>
+      <c r="G186" t="inlineStr">
+        <is>
+          <t>20208000104436429001</t>
+        </is>
+      </c>
+      <c r="H186" t="inlineStr">
+        <is>
+          <t>00987</t>
+        </is>
+      </c>
+      <c r="I186" t="inlineStr">
+        <is>
+          <t>Предоплата за товар по дог. №201/26 от 30.09.2026</t>
+        </is>
+      </c>
+      <c r="J186" s="2" t="n">
+        <v>283900000</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" s="3" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B187" t="n">
+        <v>279</v>
+      </c>
+      <c r="C187" s="2" t="n">
         <v>300000</v>
       </c>
-      <c r="D179" s="2" t="n"/>
-      <c r="E179" t="inlineStr">
+      <c r="D187" s="2" t="n"/>
+      <c r="E187" t="inlineStr">
         <is>
           <t>Zarafshon Kredit Bank</t>
         </is>
       </c>
-      <c r="G179" t="inlineStr">
+      <c r="G187" t="inlineStr">
         <is>
           <t>45994000900000001001</t>
         </is>
       </c>
-      <c r="H179" t="inlineStr">
-        <is>
-          <t>00987</t>
-        </is>
-      </c>
-      <c r="I179" t="inlineStr">
-        <is>
-          <t>Hisob-kassa xizmati uchun haq</t>
-        </is>
-      </c>
-      <c r="J179" s="2" t="n">
+      <c r="H187" t="inlineStr">
+        <is>
+          <t>00987</t>
+        </is>
+      </c>
+      <c r="I187" t="inlineStr">
+        <is>
+          <t>Плата за SMS-информирование</t>
+        </is>
+      </c>
+      <c r="J187" s="2" t="n">
         <v>283600000</v>
       </c>
     </row>
-    <row r="180">
-      <c r="A180" t="inlineStr">
+    <row r="188">
+      <c r="A188" t="inlineStr">
         <is>
           <t>Итого обороты:</t>
         </is>
       </c>
-      <c r="C180" s="4" t="n">
-        <v>3554667000</v>
-      </c>
-      <c r="D180" s="4" t="n">
-        <v>3562567000</v>
-      </c>
-    </row>
-    <row r="181">
-      <c r="A181" t="inlineStr">
+      <c r="C188" s="4" t="n">
+        <v>3501853000</v>
+      </c>
+      <c r="D188" s="4" t="n">
+        <v>3509753000</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
         <is>
           <t>Исходящий остаток на 30.09.2026:</t>
         </is>
       </c>
-      <c r="C181" s="4" t="n">
+      <c r="C189" s="4" t="n">
         <v>283600000</v>
       </c>
-      <c r="D181" s="4" t="n"/>
+      <c r="D189" s="4" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
